--- a/ROSALES/Mayo/expensas rosales MAYOxlsx.xlsx
+++ b/ROSALES/Mayo/expensas rosales MAYOxlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\ROSALES\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7271414F-ADC0-45B9-81AE-0020924F12FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1B3D1DC-1448-4D20-BFC5-8736DBFA9BD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Edesur" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$62</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$64</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">Edesur!$A$1:$N$40</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$L$37</definedName>
   </definedNames>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="135">
   <si>
     <t>TOTAL</t>
   </si>
@@ -410,9 +410,6 @@
     <t>Este mes y el anterior lo cerramos sin TSG - EL mes que viene hay que pasar 3</t>
   </si>
   <si>
-    <t>Doartero julio - reconexion de porteros electricos piso 8 y 2</t>
-  </si>
-  <si>
     <t>Desobstruccion de colectora pluvial</t>
   </si>
   <si>
@@ -426,6 +423,15 @@
   </si>
   <si>
     <t>Vto. 16/06</t>
+  </si>
+  <si>
+    <t>Matias Salvatierra - Desobstruccion de colectora pluvial</t>
+  </si>
+  <si>
+    <t>Matias Salvatierra - Desobstruccion de colectora cloacal</t>
+  </si>
+  <si>
+    <t>Casa Koruk</t>
   </si>
 </sst>
 </file>
@@ -1457,6 +1463,8 @@
     <xf numFmtId="4" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="4" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1480,8 +1488,6 @@
     <xf numFmtId="44" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1894,7 +1900,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F63"/>
+  <dimension ref="A2:F65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -1932,10 +1938,10 @@
         <v>25</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -2070,7 +2076,7 @@
         <v>121</v>
       </c>
       <c r="B26" s="42"/>
-      <c r="C26" s="234">
+      <c r="C26" s="225">
         <v>5684</v>
       </c>
       <c r="D26" s="45"/>
@@ -2089,247 +2095,259 @@
     </row>
     <row r="28" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="140" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B28" s="141"/>
-      <c r="C28" s="223">
-        <v>170000</v>
+      <c r="C28" s="225">
+        <v>56650</v>
       </c>
       <c r="D28" s="45"/>
       <c r="F28" s="12"/>
     </row>
     <row r="29" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="235" t="s">
-        <v>128</v>
+      <c r="A29" s="140" t="s">
+        <v>132</v>
       </c>
       <c r="B29" s="141"/>
-      <c r="C29" s="234">
+      <c r="C29" s="225">
+        <v>64550</v>
+      </c>
+      <c r="D29" s="45"/>
+      <c r="F29" s="12"/>
+    </row>
+    <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="226" t="s">
+        <v>134</v>
+      </c>
+      <c r="B30" s="141"/>
+      <c r="C30" s="225">
+        <v>20000</v>
+      </c>
+      <c r="D30" s="45"/>
+      <c r="F30" s="12"/>
+    </row>
+    <row r="31" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="226" t="s">
+        <v>127</v>
+      </c>
+      <c r="B31" s="141"/>
+      <c r="C31" s="225">
         <v>76654</v>
       </c>
-      <c r="D29" s="45"/>
-      <c r="F29" s="12" t="s">
+      <c r="D31" s="45"/>
+      <c r="F31" s="12" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="28" t="s">
-        <v>131</v>
-      </c>
-      <c r="B30" s="42"/>
-      <c r="C30" s="223">
+    <row r="32" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="B32" s="42"/>
+      <c r="C32" s="223">
         <v>45000</v>
       </c>
-      <c r="F30" s="12"/>
-    </row>
-    <row r="31" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="28" t="s">
+      <c r="F32" s="12"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="B31" s="39"/>
-      <c r="C31" s="34"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="12"/>
-    </row>
-    <row r="32" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="40"/>
-      <c r="B32" s="41"/>
-      <c r="C32" s="23">
-        <f>SUM(C24:C31)</f>
-        <v>916489.87</v>
-      </c>
-      <c r="F32" s="12"/>
-    </row>
-    <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="30" t="s">
+      <c r="B33" s="39"/>
+      <c r="C33" s="34"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="12"/>
+    </row>
+    <row r="34" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="40"/>
+      <c r="B34" s="41"/>
+      <c r="C34" s="23">
+        <f>SUM(C24:C33)</f>
+        <v>887689.87</v>
+      </c>
+      <c r="F34" s="12"/>
+    </row>
+    <row r="35" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B33" s="30"/>
-      <c r="C33" s="43">
-        <f>+C32+C23</f>
-        <v>1403249.71</v>
-      </c>
-      <c r="F33" s="12"/>
-    </row>
-    <row r="34" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C34" s="24"/>
-      <c r="F34" s="12"/>
-    </row>
-    <row r="35" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="13" t="s">
+      <c r="B35" s="30"/>
+      <c r="C35" s="43">
+        <f>+C34+C23</f>
+        <v>1374449.71</v>
+      </c>
+      <c r="F35" s="12"/>
+    </row>
+    <row r="36" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C36" s="24"/>
+      <c r="F36" s="12"/>
+    </row>
+    <row r="37" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A37" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C35" s="24"/>
-      <c r="F35" s="12"/>
-    </row>
-    <row r="36" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="28"/>
-      <c r="B36" s="28"/>
-      <c r="C36" s="33"/>
-      <c r="F36" s="12"/>
-    </row>
-    <row r="37" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="28"/>
-      <c r="B37" s="28"/>
-      <c r="C37" s="34"/>
+      <c r="C37" s="24"/>
       <c r="F37" s="12"/>
     </row>
     <row r="38" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="28"/>
       <c r="B38" s="28"/>
-      <c r="C38" s="34"/>
+      <c r="C38" s="33"/>
       <c r="F38" s="12"/>
     </row>
     <row r="39" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C39" s="25"/>
+      <c r="A39" s="28"/>
+      <c r="B39" s="28"/>
+      <c r="C39" s="34"/>
       <c r="F39" s="12"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="13" t="s">
+    <row r="40" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="28"/>
+      <c r="B40" s="28"/>
+      <c r="C40" s="34"/>
+      <c r="F40" s="12"/>
+    </row>
+    <row r="41" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C41" s="25"/>
+      <c r="F41" s="12"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B40" s="13"/>
-      <c r="C40" s="14">
-        <f>+C36+C37+C38+C39</f>
-        <v>0</v>
-      </c>
-      <c r="E40" s="6"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="18" t="s">
+      <c r="B42" s="13"/>
+      <c r="C42" s="14">
+        <f>+C38+C39+C40+C41</f>
+        <v>0</v>
+      </c>
+      <c r="E42" s="6"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B42" s="18"/>
-      <c r="C42" s="19">
-        <f>+C40+C33</f>
-        <v>1403249.71</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="4"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="4"/>
-      <c r="C45" s="169"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-    </row>
-    <row r="46" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B44" s="18"/>
+      <c r="C44" s="19">
+        <f>+C42+C35</f>
+        <v>1374449.71</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="4"/>
-      <c r="C46" s="169"/>
-      <c r="D46" s="6"/>
-      <c r="E46" s="6"/>
-    </row>
-    <row r="47" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="170" t="s">
-        <v>117</v>
-      </c>
-      <c r="B47" s="168"/>
-      <c r="C47" s="171">
-        <v>-108808.68868403265</v>
-      </c>
-      <c r="D47" s="6"/>
-      <c r="E47" s="6"/>
-    </row>
-    <row r="48" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="170" t="s">
-        <v>130</v>
-      </c>
-      <c r="B48" s="168"/>
-      <c r="C48" s="173">
-        <f>-(C33-C31)</f>
-        <v>-1403249.71</v>
-      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="4"/>
+      <c r="C47" s="169"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+    </row>
+    <row r="48" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="4"/>
+      <c r="C48" s="169"/>
       <c r="D48" s="6"/>
       <c r="E48" s="6"/>
     </row>
     <row r="49" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="170" t="s">
+        <v>117</v>
+      </c>
+      <c r="B49" s="168"/>
+      <c r="C49" s="171">
+        <v>-108808.68868403265</v>
+      </c>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+    </row>
+    <row r="50" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="170" t="s">
+        <v>129</v>
+      </c>
+      <c r="B50" s="168"/>
+      <c r="C50" s="173">
+        <f>-(C35-C33)</f>
+        <v>-1374449.71</v>
+      </c>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+    </row>
+    <row r="51" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="170" t="s">
         <v>119</v>
       </c>
-      <c r="B49" s="168"/>
-      <c r="C49" s="221">
+      <c r="B51" s="168"/>
+      <c r="C51" s="221">
         <f>'prorrateo '!F31</f>
         <v>880779.1571104785</v>
       </c>
     </row>
-    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="174"/>
-      <c r="C50" s="175"/>
-    </row>
-    <row r="51" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="172" t="s">
+    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="174"/>
+      <c r="C52" s="175"/>
+    </row>
+    <row r="53" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="172" t="s">
         <v>8</v>
       </c>
-      <c r="B51" s="167"/>
-      <c r="C51" s="176">
-        <f>SUM(C45:C49)</f>
-        <v>-631279.24157355423</v>
-      </c>
-      <c r="D51" s="5"/>
-    </row>
-    <row r="52" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="9"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="10"/>
-    </row>
-    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="225"/>
-      <c r="B53" s="225"/>
-      <c r="C53" s="225"/>
-      <c r="F53" s="44"/>
-    </row>
-    <row r="54" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="226"/>
-      <c r="B54" s="226"/>
-      <c r="C54" s="226"/>
-    </row>
-    <row r="55" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="26" t="s">
+      <c r="B53" s="167"/>
+      <c r="C53" s="176">
+        <f>SUM(C47:C51)</f>
+        <v>-602479.24157355423</v>
+      </c>
+      <c r="D53" s="5"/>
+    </row>
+    <row r="54" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="9"/>
+      <c r="B54" s="8"/>
+      <c r="C54" s="10"/>
+    </row>
+    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="227"/>
+      <c r="B55" s="227"/>
+      <c r="C55" s="227"/>
+      <c r="F55" s="44"/>
+    </row>
+    <row r="56" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="228"/>
+      <c r="B56" s="228"/>
+      <c r="C56" s="228"/>
+    </row>
+    <row r="57" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="B55" s="27"/>
-      <c r="C55" s="29"/>
-    </row>
-    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="28" t="s">
+      <c r="B57" s="27"/>
+      <c r="C57" s="29"/>
+    </row>
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B56" s="28"/>
-      <c r="C56" s="31">
-        <f>-C40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="28"/>
-      <c r="B57" s="28"/>
-      <c r="C57" s="31"/>
-    </row>
-    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="28"/>
       <c r="B58" s="28"/>
-      <c r="C58" s="32"/>
+      <c r="C58" s="31">
+        <f>-C42</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="177" t="s">
-        <v>0</v>
-      </c>
-      <c r="B59" s="178"/>
-      <c r="C59" s="179">
-        <f>SUM(C55:C58)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="8"/>
-      <c r="B60" s="8"/>
-      <c r="C60" s="8"/>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="8"/>
-      <c r="B61" s="8"/>
-      <c r="C61" s="8"/>
+      <c r="A59" s="28"/>
+      <c r="B59" s="28"/>
+      <c r="C59" s="31"/>
+    </row>
+    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="28"/>
+      <c r="B60" s="28"/>
+      <c r="C60" s="32"/>
+    </row>
+    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="177" t="s">
+        <v>0</v>
+      </c>
+      <c r="B61" s="178"/>
+      <c r="C61" s="179">
+        <f>SUM(C57:C60)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="8"/>
@@ -2341,9 +2359,19 @@
       <c r="B63" s="8"/>
       <c r="C63" s="8"/>
     </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" s="8"/>
+      <c r="B64" s="8"/>
+      <c r="C64" s="8"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="8"/>
+      <c r="B65" s="8"/>
+      <c r="C65" s="8"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A53:C54"/>
+    <mergeCell ref="A55:C56"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -2383,11 +2411,11 @@
       <c r="A1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="227">
+      <c r="B1" s="229">
         <f>D1</f>
         <v>1436145.71</v>
       </c>
-      <c r="C1" s="227"/>
+      <c r="C1" s="229"/>
       <c r="D1" s="145">
         <v>1436145.71</v>
       </c>
@@ -3542,62 +3570,62 @@
       <c r="J32" s="22"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" s="228" t="s">
+      <c r="A33" s="230" t="s">
         <v>123</v>
       </c>
-      <c r="B33" s="228"/>
-      <c r="C33" s="228"/>
-      <c r="D33" s="228"/>
-      <c r="E33" s="228"/>
-      <c r="F33" s="228"/>
-      <c r="G33" s="228"/>
-      <c r="H33" s="228"/>
-      <c r="I33" s="228"/>
-      <c r="J33" s="228"/>
-      <c r="K33" s="228"/>
-      <c r="L33" s="228"/>
+      <c r="B33" s="230"/>
+      <c r="C33" s="230"/>
+      <c r="D33" s="230"/>
+      <c r="E33" s="230"/>
+      <c r="F33" s="230"/>
+      <c r="G33" s="230"/>
+      <c r="H33" s="230"/>
+      <c r="I33" s="230"/>
+      <c r="J33" s="230"/>
+      <c r="K33" s="230"/>
+      <c r="L33" s="230"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" s="228"/>
-      <c r="B34" s="228"/>
-      <c r="C34" s="228"/>
-      <c r="D34" s="228"/>
-      <c r="E34" s="228"/>
-      <c r="F34" s="228"/>
-      <c r="G34" s="228"/>
-      <c r="H34" s="228"/>
-      <c r="I34" s="228"/>
-      <c r="J34" s="228"/>
-      <c r="K34" s="228"/>
-      <c r="L34" s="228"/>
+      <c r="A34" s="230"/>
+      <c r="B34" s="230"/>
+      <c r="C34" s="230"/>
+      <c r="D34" s="230"/>
+      <c r="E34" s="230"/>
+      <c r="F34" s="230"/>
+      <c r="G34" s="230"/>
+      <c r="H34" s="230"/>
+      <c r="I34" s="230"/>
+      <c r="J34" s="230"/>
+      <c r="K34" s="230"/>
+      <c r="L34" s="230"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" s="228"/>
-      <c r="B35" s="228"/>
-      <c r="C35" s="228"/>
-      <c r="D35" s="228"/>
-      <c r="E35" s="228"/>
-      <c r="F35" s="228"/>
-      <c r="G35" s="228"/>
-      <c r="H35" s="228"/>
-      <c r="I35" s="228"/>
-      <c r="J35" s="228"/>
-      <c r="K35" s="228"/>
-      <c r="L35" s="228"/>
+      <c r="A35" s="230"/>
+      <c r="B35" s="230"/>
+      <c r="C35" s="230"/>
+      <c r="D35" s="230"/>
+      <c r="E35" s="230"/>
+      <c r="F35" s="230"/>
+      <c r="G35" s="230"/>
+      <c r="H35" s="230"/>
+      <c r="I35" s="230"/>
+      <c r="J35" s="230"/>
+      <c r="K35" s="230"/>
+      <c r="L35" s="230"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="228"/>
-      <c r="B36" s="228"/>
-      <c r="C36" s="228"/>
-      <c r="D36" s="228"/>
-      <c r="E36" s="228"/>
-      <c r="F36" s="228"/>
-      <c r="G36" s="228"/>
-      <c r="H36" s="228"/>
-      <c r="I36" s="228"/>
-      <c r="J36" s="228"/>
-      <c r="K36" s="228"/>
-      <c r="L36" s="228"/>
+      <c r="A36" s="230"/>
+      <c r="B36" s="230"/>
+      <c r="C36" s="230"/>
+      <c r="D36" s="230"/>
+      <c r="E36" s="230"/>
+      <c r="F36" s="230"/>
+      <c r="G36" s="230"/>
+      <c r="H36" s="230"/>
+      <c r="I36" s="230"/>
+      <c r="J36" s="230"/>
+      <c r="K36" s="230"/>
+      <c r="L36" s="230"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E40" s="21"/>
@@ -3636,22 +3664,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="229" t="s">
+      <c r="A1" s="231" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="230"/>
-      <c r="C1" s="230"/>
-      <c r="D1" s="230"/>
-      <c r="E1" s="230"/>
-      <c r="F1" s="230"/>
-      <c r="G1" s="230"/>
-      <c r="H1" s="230"/>
-      <c r="I1" s="230"/>
-      <c r="J1" s="230"/>
-      <c r="K1" s="230"/>
-      <c r="L1" s="230"/>
-      <c r="M1" s="230"/>
-      <c r="N1" s="231"/>
+      <c r="B1" s="232"/>
+      <c r="C1" s="232"/>
+      <c r="D1" s="232"/>
+      <c r="E1" s="232"/>
+      <c r="F1" s="232"/>
+      <c r="G1" s="232"/>
+      <c r="H1" s="232"/>
+      <c r="I1" s="232"/>
+      <c r="J1" s="232"/>
+      <c r="K1" s="232"/>
+      <c r="L1" s="232"/>
+      <c r="M1" s="232"/>
+      <c r="N1" s="233"/>
       <c r="O1" s="78"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
@@ -3789,11 +3817,11 @@
         <f>C8-J38</f>
         <v>-142678.16310000012</v>
       </c>
-      <c r="L8" s="233">
+      <c r="L8" s="235">
         <f>C7-J38</f>
         <v>672848.54689999984</v>
       </c>
-      <c r="M8" s="233"/>
+      <c r="M8" s="235"/>
       <c r="N8" s="86"/>
       <c r="O8" s="80"/>
       <c r="P8" s="11"/>
@@ -5226,18 +5254,18 @@
       <c r="A40" s="97" t="s">
         <v>110</v>
       </c>
-      <c r="C40" s="232"/>
-      <c r="D40" s="230"/>
-      <c r="E40" s="230"/>
-      <c r="F40" s="230"/>
-      <c r="G40" s="230"/>
-      <c r="H40" s="230"/>
-      <c r="I40" s="230"/>
-      <c r="J40" s="230"/>
-      <c r="K40" s="230"/>
-      <c r="L40" s="230"/>
-      <c r="M40" s="230"/>
-      <c r="N40" s="230"/>
+      <c r="C40" s="234"/>
+      <c r="D40" s="232"/>
+      <c r="E40" s="232"/>
+      <c r="F40" s="232"/>
+      <c r="G40" s="232"/>
+      <c r="H40" s="232"/>
+      <c r="I40" s="232"/>
+      <c r="J40" s="232"/>
+      <c r="K40" s="232"/>
+      <c r="L40" s="232"/>
+      <c r="M40" s="232"/>
+      <c r="N40" s="232"/>
       <c r="O40" s="97"/>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.3">

--- a/ROSALES/Mayo/expensas rosales MAYOxlsx.xlsx
+++ b/ROSALES/Mayo/expensas rosales MAYOxlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\ROSALES\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1B3D1DC-1448-4D20-BFC5-8736DBFA9BD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{832D8420-3886-4DFC-A4D4-E3FB5C1B71BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -667,7 +667,7 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1456,7 +1456,6 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="10" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="26" fillId="10" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="31" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="171" fontId="25" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -1488,6 +1487,7 @@
     <xf numFmtId="44" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="171" fontId="31" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1993,7 +1993,7 @@
         <v>26</v>
       </c>
       <c r="B18" s="38"/>
-      <c r="C18" s="223">
+      <c r="C18" s="222">
         <v>41473</v>
       </c>
       <c r="D18" s="4"/>
@@ -2002,7 +2002,7 @@
     <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="28"/>
       <c r="B19" s="39"/>
-      <c r="C19" s="223"/>
+      <c r="C19" s="222"/>
       <c r="D19" s="4"/>
       <c r="E19" s="6"/>
       <c r="F19" s="8"/>
@@ -2012,7 +2012,7 @@
         <v>10</v>
       </c>
       <c r="B20" s="39"/>
-      <c r="C20" s="224">
+      <c r="C20" s="223">
         <v>301604.38</v>
       </c>
       <c r="D20" s="20"/>
@@ -2023,7 +2023,7 @@
         <v>27</v>
       </c>
       <c r="B21" s="39"/>
-      <c r="C21" s="223">
+      <c r="C21" s="222">
         <v>65000</v>
       </c>
       <c r="D21" s="20"/>
@@ -2036,7 +2036,7 @@
       <c r="B22" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="223">
+      <c r="C22" s="222">
         <v>78682.460000000006</v>
       </c>
       <c r="D22" s="4"/>
@@ -2065,7 +2065,7 @@
         <v>120</v>
       </c>
       <c r="B25" s="42"/>
-      <c r="C25" s="223">
+      <c r="C25" s="222">
         <v>349151.87</v>
       </c>
       <c r="D25" s="45"/>
@@ -2076,7 +2076,7 @@
         <v>121</v>
       </c>
       <c r="B26" s="42"/>
-      <c r="C26" s="225">
+      <c r="C26" s="224">
         <v>5684</v>
       </c>
       <c r="D26" s="45"/>
@@ -2087,7 +2087,7 @@
         <v>125</v>
       </c>
       <c r="B27" s="141"/>
-      <c r="C27" s="223">
+      <c r="C27" s="222">
         <v>270000</v>
       </c>
       <c r="D27" s="45"/>
@@ -2098,7 +2098,7 @@
         <v>133</v>
       </c>
       <c r="B28" s="141"/>
-      <c r="C28" s="225">
+      <c r="C28" s="224">
         <v>56650</v>
       </c>
       <c r="D28" s="45"/>
@@ -2109,29 +2109,29 @@
         <v>132</v>
       </c>
       <c r="B29" s="141"/>
-      <c r="C29" s="225">
+      <c r="C29" s="224">
         <v>64550</v>
       </c>
       <c r="D29" s="45"/>
       <c r="F29" s="12"/>
     </row>
     <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="226" t="s">
+      <c r="A30" s="225" t="s">
         <v>134</v>
       </c>
       <c r="B30" s="141"/>
-      <c r="C30" s="225">
+      <c r="C30" s="224">
         <v>20000</v>
       </c>
       <c r="D30" s="45"/>
       <c r="F30" s="12"/>
     </row>
     <row r="31" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="226" t="s">
+      <c r="A31" s="225" t="s">
         <v>127</v>
       </c>
       <c r="B31" s="141"/>
-      <c r="C31" s="225">
+      <c r="C31" s="224">
         <v>76654</v>
       </c>
       <c r="D31" s="45"/>
@@ -2144,7 +2144,7 @@
         <v>130</v>
       </c>
       <c r="B32" s="42"/>
-      <c r="C32" s="223">
+      <c r="C32" s="222">
         <v>45000</v>
       </c>
       <c r="F32" s="12"/>
@@ -2276,7 +2276,7 @@
         <v>119</v>
       </c>
       <c r="B51" s="168"/>
-      <c r="C51" s="221">
+      <c r="C51" s="220">
         <f>'prorrateo '!F31</f>
         <v>880779.1571104785</v>
       </c>
@@ -2302,15 +2302,15 @@
       <c r="C54" s="10"/>
     </row>
     <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="227"/>
-      <c r="B55" s="227"/>
-      <c r="C55" s="227"/>
+      <c r="A55" s="226"/>
+      <c r="B55" s="226"/>
+      <c r="C55" s="226"/>
       <c r="F55" s="44"/>
     </row>
     <row r="56" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="228"/>
-      <c r="B56" s="228"/>
-      <c r="C56" s="228"/>
+      <c r="A56" s="227"/>
+      <c r="B56" s="227"/>
+      <c r="C56" s="227"/>
     </row>
     <row r="57" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="26" t="s">
@@ -2411,11 +2411,11 @@
       <c r="A1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="229">
+      <c r="B1" s="228">
         <f>D1</f>
         <v>1436145.71</v>
       </c>
-      <c r="C1" s="229"/>
+      <c r="C1" s="228"/>
       <c r="D1" s="145">
         <v>1436145.71</v>
       </c>
@@ -3570,62 +3570,62 @@
       <c r="J32" s="22"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" s="230" t="s">
+      <c r="A33" s="229" t="s">
         <v>123</v>
       </c>
-      <c r="B33" s="230"/>
-      <c r="C33" s="230"/>
-      <c r="D33" s="230"/>
-      <c r="E33" s="230"/>
-      <c r="F33" s="230"/>
-      <c r="G33" s="230"/>
-      <c r="H33" s="230"/>
-      <c r="I33" s="230"/>
-      <c r="J33" s="230"/>
-      <c r="K33" s="230"/>
-      <c r="L33" s="230"/>
+      <c r="B33" s="229"/>
+      <c r="C33" s="229"/>
+      <c r="D33" s="229"/>
+      <c r="E33" s="229"/>
+      <c r="F33" s="229"/>
+      <c r="G33" s="229"/>
+      <c r="H33" s="229"/>
+      <c r="I33" s="229"/>
+      <c r="J33" s="229"/>
+      <c r="K33" s="229"/>
+      <c r="L33" s="229"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" s="230"/>
-      <c r="B34" s="230"/>
-      <c r="C34" s="230"/>
-      <c r="D34" s="230"/>
-      <c r="E34" s="230"/>
-      <c r="F34" s="230"/>
-      <c r="G34" s="230"/>
-      <c r="H34" s="230"/>
-      <c r="I34" s="230"/>
-      <c r="J34" s="230"/>
-      <c r="K34" s="230"/>
-      <c r="L34" s="230"/>
+      <c r="A34" s="229"/>
+      <c r="B34" s="229"/>
+      <c r="C34" s="229"/>
+      <c r="D34" s="229"/>
+      <c r="E34" s="229"/>
+      <c r="F34" s="229"/>
+      <c r="G34" s="229"/>
+      <c r="H34" s="229"/>
+      <c r="I34" s="229"/>
+      <c r="J34" s="229"/>
+      <c r="K34" s="229"/>
+      <c r="L34" s="229"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" s="230"/>
-      <c r="B35" s="230"/>
-      <c r="C35" s="230"/>
-      <c r="D35" s="230"/>
-      <c r="E35" s="230"/>
-      <c r="F35" s="230"/>
-      <c r="G35" s="230"/>
-      <c r="H35" s="230"/>
-      <c r="I35" s="230"/>
-      <c r="J35" s="230"/>
-      <c r="K35" s="230"/>
-      <c r="L35" s="230"/>
+      <c r="A35" s="229"/>
+      <c r="B35" s="229"/>
+      <c r="C35" s="229"/>
+      <c r="D35" s="229"/>
+      <c r="E35" s="229"/>
+      <c r="F35" s="229"/>
+      <c r="G35" s="229"/>
+      <c r="H35" s="229"/>
+      <c r="I35" s="229"/>
+      <c r="J35" s="229"/>
+      <c r="K35" s="229"/>
+      <c r="L35" s="229"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="230"/>
-      <c r="B36" s="230"/>
-      <c r="C36" s="230"/>
-      <c r="D36" s="230"/>
-      <c r="E36" s="230"/>
-      <c r="F36" s="230"/>
-      <c r="G36" s="230"/>
-      <c r="H36" s="230"/>
-      <c r="I36" s="230"/>
-      <c r="J36" s="230"/>
-      <c r="K36" s="230"/>
-      <c r="L36" s="230"/>
+      <c r="A36" s="229"/>
+      <c r="B36" s="229"/>
+      <c r="C36" s="229"/>
+      <c r="D36" s="229"/>
+      <c r="E36" s="229"/>
+      <c r="F36" s="229"/>
+      <c r="G36" s="229"/>
+      <c r="H36" s="229"/>
+      <c r="I36" s="229"/>
+      <c r="J36" s="229"/>
+      <c r="K36" s="229"/>
+      <c r="L36" s="229"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E40" s="21"/>
@@ -3664,22 +3664,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="231" t="s">
+      <c r="A1" s="230" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="232"/>
-      <c r="C1" s="232"/>
-      <c r="D1" s="232"/>
-      <c r="E1" s="232"/>
-      <c r="F1" s="232"/>
-      <c r="G1" s="232"/>
-      <c r="H1" s="232"/>
-      <c r="I1" s="232"/>
-      <c r="J1" s="232"/>
-      <c r="K1" s="232"/>
-      <c r="L1" s="232"/>
-      <c r="M1" s="232"/>
-      <c r="N1" s="233"/>
+      <c r="B1" s="231"/>
+      <c r="C1" s="231"/>
+      <c r="D1" s="231"/>
+      <c r="E1" s="231"/>
+      <c r="F1" s="231"/>
+      <c r="G1" s="231"/>
+      <c r="H1" s="231"/>
+      <c r="I1" s="231"/>
+      <c r="J1" s="231"/>
+      <c r="K1" s="231"/>
+      <c r="L1" s="231"/>
+      <c r="M1" s="231"/>
+      <c r="N1" s="232"/>
       <c r="O1" s="78"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
@@ -3779,8 +3779,8 @@
       <c r="B7" s="83" t="s">
         <v>84</v>
       </c>
-      <c r="C7" s="220">
-        <v>815526.71</v>
+      <c r="C7" s="235">
+        <v>804174.23</v>
       </c>
       <c r="D7" s="28"/>
       <c r="E7" s="184"/>
@@ -3817,11 +3817,11 @@
         <f>C8-J38</f>
         <v>-142678.16310000012</v>
       </c>
-      <c r="L8" s="235">
+      <c r="L8" s="234">
         <f>C7-J38</f>
-        <v>672848.54689999984</v>
-      </c>
-      <c r="M8" s="235"/>
+        <v>661496.06689999986</v>
+      </c>
+      <c r="M8" s="234"/>
       <c r="N8" s="86"/>
       <c r="O8" s="80"/>
       <c r="P8" s="11"/>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="L10" s="129">
         <f>L$8*E10/S$12</f>
-        <v>34382.560746589996</v>
+        <v>33802.449018589992</v>
       </c>
       <c r="M10" s="109">
         <f>G10-F10</f>
@@ -3919,11 +3919,11 @@
       </c>
       <c r="N10" s="106">
         <f>J10+L10</f>
-        <v>43845.669046589959</v>
+        <v>43265.557318589956</v>
       </c>
       <c r="O10" s="99">
         <f>N10+'prorrateo '!L3</f>
-        <v>117232.71482758997</v>
+        <v>116652.60309958996</v>
       </c>
       <c r="P10" s="11"/>
     </row>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="L11" s="129">
         <f t="shared" ref="L11:L36" si="3">L$8*E11/S$12</f>
-        <v>34247.991037209991</v>
+        <v>33670.149805209992</v>
       </c>
       <c r="M11" s="109">
         <f t="shared" ref="M11:M26" si="4">G11-F11</f>
@@ -3975,11 +3975,11 @@
       </c>
       <c r="N11" s="106">
         <f t="shared" ref="N11:N25" si="5">J11+L11</f>
-        <v>39387.518637210007</v>
+        <v>38809.677405210008</v>
       </c>
       <c r="O11" s="99">
         <f>N11+'prorrateo '!L4</f>
-        <v>112487.33527621001</v>
+        <v>111909.49404421001</v>
       </c>
       <c r="P11" s="11"/>
     </row>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="L12" s="129">
         <f t="shared" si="3"/>
-        <v>33911.566763759991</v>
+        <v>33339.401771759993</v>
       </c>
       <c r="M12" s="109">
         <f>G12-F12</f>
@@ -4031,11 +4031,11 @@
       </c>
       <c r="N12" s="106">
         <f t="shared" si="5"/>
-        <v>37756.833763759991</v>
+        <v>37184.668771759993</v>
       </c>
       <c r="O12" s="99">
         <f>N12+'prorrateo '!L5</f>
-        <v>110138.57754775998</v>
+        <v>109566.41255575998</v>
       </c>
       <c r="P12" s="11"/>
       <c r="S12">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="L13" s="129">
         <f t="shared" si="3"/>
-        <v>35055.409293489989</v>
+        <v>34463.945085489991</v>
       </c>
       <c r="M13" s="191">
         <f t="shared" si="4"/>
@@ -4090,11 +4090,11 @@
       </c>
       <c r="N13" s="106">
         <f t="shared" si="5"/>
-        <v>40232.45169348998</v>
+        <v>39640.987485489983</v>
       </c>
       <c r="O13" s="99">
         <f>N13+'prorrateo '!L6</f>
-        <v>115055.64318448998</v>
+        <v>114464.17897648999</v>
       </c>
       <c r="P13" s="11"/>
     </row>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="L14" s="129">
         <f t="shared" si="3"/>
-        <v>34382.560746589996</v>
+        <v>33802.449018589992</v>
       </c>
       <c r="M14" s="109">
         <f t="shared" si="4"/>
@@ -4146,11 +4146,11 @@
       </c>
       <c r="N14" s="106">
         <f t="shared" si="5"/>
-        <v>42044.958646589999</v>
+        <v>41464.846918589996</v>
       </c>
       <c r="O14" s="99">
         <f>N14+'prorrateo '!L7</f>
-        <v>115432.00442759</v>
+        <v>114851.89269959001</v>
       </c>
       <c r="P14" s="11"/>
     </row>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="L15" s="129">
         <f t="shared" si="3"/>
-        <v>34247.991037209991</v>
+        <v>33670.149805209992</v>
       </c>
       <c r="M15" s="109">
         <f t="shared" si="4"/>
@@ -4202,11 +4202,11 @@
       </c>
       <c r="N15" s="106">
         <f t="shared" si="5"/>
-        <v>42501.247037209992</v>
+        <v>41923.405805209994</v>
       </c>
       <c r="O15" s="99">
         <f>N15+'prorrateo '!L8</f>
-        <v>115601.06367620999</v>
+        <v>115023.22244421</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="L16" s="129">
         <f t="shared" si="3"/>
-        <v>34382.560746589996</v>
+        <v>33802.449018589992</v>
       </c>
       <c r="M16" s="109">
         <f t="shared" si="4"/>
@@ -4257,11 +4257,11 @@
       </c>
       <c r="N16" s="106">
         <f t="shared" si="5"/>
-        <v>40281.763046590007</v>
+        <v>39701.651318590004</v>
       </c>
       <c r="O16" s="99">
         <f>N16+'prorrateo '!L9</f>
-        <v>113668.80882759002</v>
+        <v>113088.69709959</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="L17" s="215">
         <f t="shared" si="3"/>
-        <v>34247.991037209991</v>
+        <v>33670.149805209992</v>
       </c>
       <c r="M17" s="216">
         <f t="shared" si="4"/>
@@ -4312,11 +4312,11 @@
       </c>
       <c r="N17" s="211">
         <f t="shared" si="5"/>
-        <v>43617.312337210002</v>
+        <v>43039.471105210003</v>
       </c>
       <c r="O17" s="99">
         <f>N17+'prorrateo '!L10</f>
-        <v>384003.56153601955</v>
+        <v>383425.72030401957</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="L18" s="129">
         <f t="shared" si="3"/>
-        <v>33911.566763759991</v>
+        <v>33339.401771759993</v>
       </c>
       <c r="M18" s="109">
         <f t="shared" si="4"/>
@@ -4367,11 +4367,11 @@
       </c>
       <c r="N18" s="106">
         <f t="shared" si="5"/>
-        <v>40373.491063759982</v>
+        <v>39801.326071759977</v>
       </c>
       <c r="O18" s="99">
         <f>N18+'prorrateo '!L11</f>
-        <v>112755.23484775997</v>
+        <v>112183.06985575997</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="L19" s="129">
         <f t="shared" si="3"/>
-        <v>35055.409293489989</v>
+        <v>34463.945085489991</v>
       </c>
       <c r="M19" s="109">
         <f>G19-F19</f>
@@ -4422,11 +4422,11 @@
       </c>
       <c r="N19" s="106">
         <f t="shared" si="5"/>
-        <v>52396.625593489996</v>
+        <v>51805.161385490006</v>
       </c>
       <c r="O19" s="99">
         <f>N19+'prorrateo '!L12</f>
-        <v>127219.81708449</v>
+        <v>126628.35287649001</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="L20" s="129">
         <f t="shared" si="3"/>
-        <v>34382.560746589996</v>
+        <v>33802.449018589992</v>
       </c>
       <c r="M20" s="109">
         <f t="shared" si="4"/>
@@ -4477,11 +4477,11 @@
       </c>
       <c r="N20" s="106">
         <f t="shared" si="5"/>
-        <v>52211.469446590032</v>
+        <v>51631.357718590029</v>
       </c>
       <c r="O20" s="99">
         <f>N20+'prorrateo '!L13</f>
-        <v>125598.51522759005</v>
+        <v>125018.40349959003</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="L21" s="129">
         <f t="shared" si="3"/>
-        <v>34247.991037209991</v>
+        <v>33670.149805209992</v>
       </c>
       <c r="M21" s="109">
         <f t="shared" si="4"/>
@@ -4532,11 +4532,11 @@
       </c>
       <c r="N21" s="106">
         <f t="shared" si="5"/>
-        <v>34257.369737209985</v>
+        <v>33679.528505209986</v>
       </c>
       <c r="O21" s="99">
         <f>N21+'prorrateo '!L14</f>
-        <v>107357.18637620998</v>
+        <v>106779.34514420998</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="L22" s="162">
         <f t="shared" si="3"/>
-        <v>33911.566763759991</v>
+        <v>33339.401771759993</v>
       </c>
       <c r="M22" s="163">
         <f t="shared" si="4"/>
@@ -4587,11 +4587,11 @@
       </c>
       <c r="N22" s="158">
         <f t="shared" si="5"/>
-        <v>40842.426063760002</v>
+        <v>40270.261071760004</v>
       </c>
       <c r="O22" s="99">
         <f>N22+'prorrateo '!L15</f>
-        <v>255108.35683621082</v>
+        <v>254536.19184421081</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="L23" s="129">
         <f t="shared" si="3"/>
-        <v>35055.409293489989</v>
+        <v>34463.945085489991</v>
       </c>
       <c r="M23" s="109">
         <f t="shared" si="4"/>
@@ -4642,11 +4642,11 @@
       </c>
       <c r="N23" s="106">
         <f t="shared" si="5"/>
-        <v>46966.35829348999</v>
+        <v>46374.894085489992</v>
       </c>
       <c r="O23" s="99">
         <f>N23+'prorrateo '!L16</f>
-        <v>121789.54978448999</v>
+        <v>121198.08557649</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="L24" s="129">
         <f t="shared" si="3"/>
-        <v>33911.566763759991</v>
+        <v>33339.401771759993</v>
       </c>
       <c r="M24" s="109">
         <f t="shared" si="4"/>
@@ -4697,11 +4697,11 @@
       </c>
       <c r="N24" s="106">
         <f t="shared" si="5"/>
-        <v>38460.236263759987</v>
+        <v>37888.071271759996</v>
       </c>
       <c r="O24" s="99">
         <f>N24+'prorrateo '!L17</f>
-        <v>110841.98004775998</v>
+        <v>110269.81505575999</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="L25" s="129">
         <f t="shared" si="3"/>
-        <v>35055.409293489989</v>
+        <v>34463.945085489991</v>
       </c>
       <c r="M25" s="109">
         <f t="shared" si="4"/>
@@ -4752,11 +4752,11 @@
       </c>
       <c r="N25" s="106">
         <f t="shared" si="5"/>
-        <v>43580.647593490001</v>
+        <v>42989.183385490003</v>
       </c>
       <c r="O25" s="99">
         <f>N25+'prorrateo '!L18</f>
-        <v>118403.83908449</v>
+        <v>117812.37487649001</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="L26" s="129">
         <f t="shared" si="3"/>
-        <v>49790.79247059999</v>
+        <v>48950.70895059999</v>
       </c>
       <c r="M26" s="109">
         <f t="shared" si="4"/>
@@ -4807,11 +4807,11 @@
       </c>
       <c r="N26" s="106">
         <f>J26+L26</f>
-        <v>64102.688670600022</v>
+        <v>63262.605150600022</v>
       </c>
       <c r="O26" s="99">
         <f>N26+'prorrateo '!L19</f>
-        <v>170377.47121060002</v>
+        <v>169537.38769060001</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -4844,18 +4844,18 @@
       <c r="K27" s="214"/>
       <c r="L27" s="215">
         <f t="shared" si="3"/>
-        <v>7266.7643065199991</v>
+        <v>7144.1575225199995</v>
       </c>
       <c r="M27" s="216">
         <v>0</v>
       </c>
       <c r="N27" s="211">
         <f t="shared" ref="N27:N37" si="6">J27+L27</f>
-        <v>7266.7643065199991</v>
+        <v>7144.1575225199995</v>
       </c>
       <c r="O27" s="99">
         <f>N27+'prorrateo '!L20</f>
-        <v>79490.172780923604</v>
+        <v>79367.5659969236</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
@@ -4883,18 +4883,18 @@
       <c r="K28" s="108"/>
       <c r="L28" s="129">
         <f t="shared" si="3"/>
-        <v>7266.7643065199991</v>
+        <v>7144.1575225199995</v>
       </c>
       <c r="M28" s="109">
         <v>0</v>
       </c>
       <c r="N28" s="106">
         <f t="shared" si="6"/>
-        <v>7266.7643065199991</v>
+        <v>7144.1575225199995</v>
       </c>
       <c r="O28" s="99">
         <f>N28+'prorrateo '!L21</f>
-        <v>22777.137974519999</v>
+        <v>22654.53119052</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
@@ -4915,18 +4915,18 @@
       <c r="K29" s="161"/>
       <c r="L29" s="162">
         <f t="shared" si="3"/>
-        <v>7266.7643065199991</v>
+        <v>7144.1575225199995</v>
       </c>
       <c r="M29" s="163">
         <v>0</v>
       </c>
       <c r="N29" s="158">
         <f t="shared" si="6"/>
-        <v>7266.7643065199991</v>
+        <v>7144.1575225199995</v>
       </c>
       <c r="O29" s="99">
         <f>N29+'prorrateo '!L22</f>
-        <v>79490.172780923604</v>
+        <v>79367.5659969236</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
@@ -4947,18 +4947,18 @@
       <c r="K30" s="108"/>
       <c r="L30" s="129">
         <f t="shared" si="3"/>
-        <v>7266.7643065199991</v>
+        <v>7144.1575225199995</v>
       </c>
       <c r="M30" s="109">
         <v>0</v>
       </c>
       <c r="N30" s="106">
         <f t="shared" si="6"/>
-        <v>7266.7643065199991</v>
+        <v>7144.1575225199995</v>
       </c>
       <c r="O30" s="99">
         <f>N30+'prorrateo '!L23</f>
-        <v>22777.137974519999</v>
+        <v>22654.53119052</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
@@ -4979,18 +4979,18 @@
       <c r="K31" s="108"/>
       <c r="L31" s="129">
         <f t="shared" si="3"/>
-        <v>7266.7643065199991</v>
+        <v>7144.1575225199995</v>
       </c>
       <c r="M31" s="109">
         <v>0</v>
       </c>
       <c r="N31" s="106">
         <f t="shared" si="6"/>
-        <v>7266.7643065199991</v>
+        <v>7144.1575225199995</v>
       </c>
       <c r="O31" s="99">
         <f>N31+'prorrateo '!L24</f>
-        <v>22777.137974519999</v>
+        <v>22654.53119052</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
@@ -5011,18 +5011,18 @@
       <c r="K32" s="115"/>
       <c r="L32" s="129">
         <f t="shared" si="3"/>
-        <v>7266.7643065199991</v>
+        <v>7144.1575225199995</v>
       </c>
       <c r="M32" s="109">
         <v>0</v>
       </c>
       <c r="N32" s="106">
         <f t="shared" si="6"/>
-        <v>7266.7643065199991</v>
+        <v>7144.1575225199995</v>
       </c>
       <c r="O32" s="99">
         <f>N32+'prorrateo '!L25</f>
-        <v>22777.137974519999</v>
+        <v>22654.53119052</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.3">
@@ -5043,18 +5043,18 @@
       <c r="K33" s="115"/>
       <c r="L33" s="129">
         <f t="shared" si="3"/>
-        <v>7266.7643065199991</v>
+        <v>7144.1575225199995</v>
       </c>
       <c r="M33" s="109">
         <v>0</v>
       </c>
       <c r="N33" s="106">
         <f t="shared" si="6"/>
-        <v>7266.7643065199991</v>
+        <v>7144.1575225199995</v>
       </c>
       <c r="O33" s="99">
         <f>N33+'prorrateo '!L26</f>
-        <v>22777.137974519999</v>
+        <v>22654.53119052</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.3">
@@ -5075,18 +5075,18 @@
       <c r="K34" s="115"/>
       <c r="L34" s="129">
         <f t="shared" si="3"/>
-        <v>7266.7643065199991</v>
+        <v>7144.1575225199995</v>
       </c>
       <c r="M34" s="109">
         <v>0</v>
       </c>
       <c r="N34" s="106">
         <f t="shared" si="6"/>
-        <v>7266.7643065199991</v>
+        <v>7144.1575225199995</v>
       </c>
       <c r="O34" s="99">
         <f>N34+'prorrateo '!L27</f>
-        <v>22777.137974519999</v>
+        <v>22654.53119052</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.3">
@@ -5110,22 +5110,22 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J35" s="222"/>
+      <c r="J35" s="221"/>
       <c r="K35" s="108"/>
       <c r="L35" s="129">
         <f t="shared" si="3"/>
-        <v>7266.7643065199991</v>
+        <v>7144.1575225199995</v>
       </c>
       <c r="M35" s="109">
         <v>0</v>
       </c>
       <c r="N35" s="106">
         <f t="shared" si="6"/>
-        <v>7266.7643065199991</v>
+        <v>7144.1575225199995</v>
       </c>
       <c r="O35" s="99">
         <f>N35+'prorrateo '!L28</f>
-        <v>22777.137974519999</v>
+        <v>22654.53119052</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.3">
@@ -5153,18 +5153,18 @@
       <c r="K36" s="161"/>
       <c r="L36" s="162">
         <f t="shared" si="3"/>
-        <v>7266.7643065199991</v>
+        <v>7144.1575225199995</v>
       </c>
       <c r="M36" s="163">
         <v>0</v>
       </c>
       <c r="N36" s="158">
         <f t="shared" si="6"/>
-        <v>7266.7643065199991</v>
+        <v>7144.1575225199995</v>
       </c>
       <c r="O36" s="99">
         <f>N36+'prorrateo '!L29</f>
-        <v>42321.886897003191</v>
+        <v>42199.280113003195</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.3">
@@ -5216,12 +5216,12 @@
       <c r="K38" s="115"/>
       <c r="L38" s="115">
         <f>SUM(L10:L37)</f>
-        <v>672848.54689999984</v>
+        <v>661496.06690000033</v>
       </c>
       <c r="M38" s="116"/>
       <c r="N38" s="112">
         <f>SUM(N10:N37)</f>
-        <v>815526.71</v>
+        <v>804174.23000000045</v>
       </c>
       <c r="P38" s="44"/>
     </row>
@@ -5244,7 +5244,7 @@
       <c r="K39" s="96"/>
       <c r="L39" s="135">
         <f>L38+J38</f>
-        <v>815526.71</v>
+        <v>804174.23000000045</v>
       </c>
       <c r="M39" s="95"/>
       <c r="N39" s="95"/>
@@ -5254,18 +5254,18 @@
       <c r="A40" s="97" t="s">
         <v>110</v>
       </c>
-      <c r="C40" s="234"/>
-      <c r="D40" s="232"/>
-      <c r="E40" s="232"/>
-      <c r="F40" s="232"/>
-      <c r="G40" s="232"/>
-      <c r="H40" s="232"/>
-      <c r="I40" s="232"/>
-      <c r="J40" s="232"/>
-      <c r="K40" s="232"/>
-      <c r="L40" s="232"/>
-      <c r="M40" s="232"/>
-      <c r="N40" s="232"/>
+      <c r="C40" s="233"/>
+      <c r="D40" s="231"/>
+      <c r="E40" s="231"/>
+      <c r="F40" s="231"/>
+      <c r="G40" s="231"/>
+      <c r="H40" s="231"/>
+      <c r="I40" s="231"/>
+      <c r="J40" s="231"/>
+      <c r="K40" s="231"/>
+      <c r="L40" s="231"/>
+      <c r="M40" s="231"/>
+      <c r="N40" s="231"/>
       <c r="O40" s="97"/>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.3">

--- a/ROSALES/Mayo/expensas rosales MAYOxlsx.xlsx
+++ b/ROSALES/Mayo/expensas rosales MAYOxlsx.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\ROSALES\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\ROSALES\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{832D8420-3886-4DFC-A4D4-E3FB5C1B71BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{541D1DF3-A7B3-43A7-AE9B-25D2AEC08979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Edesur" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$64</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$63</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">Edesur!$A$1:$N$40</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$L$37</definedName>
   </definedNames>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="135">
   <si>
     <t>TOTAL</t>
   </si>
@@ -107,9 +107,6 @@
     <t>EDIFICIO ROSALES 624</t>
   </si>
   <si>
-    <t>Seguro de consorcio obligatorio - cuota 1 federacion patronal - poliza nro. 2027630</t>
-  </si>
-  <si>
     <t>Ascensores Lema</t>
   </si>
   <si>
@@ -125,12 +122,6 @@
     <t>SALDO</t>
   </si>
   <si>
-    <t>SALDO EXPENSA</t>
-  </si>
-  <si>
-    <t>Gastos part</t>
-  </si>
-  <si>
     <t>A PAGAR</t>
   </si>
   <si>
@@ -143,9 +134,6 @@
     <t>Gnecchi Nicolas</t>
   </si>
   <si>
-    <t xml:space="preserve">Martina </t>
-  </si>
-  <si>
     <t>1ro. "B"</t>
   </si>
   <si>
@@ -275,9 +263,6 @@
     <t>TOTAL  EXPENSAS</t>
   </si>
   <si>
-    <t>Expensas ordinarias</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
@@ -380,9 +365,6 @@
     <t>Leandro</t>
   </si>
   <si>
-    <t>GASTOS RECUPERADOS DEL MES DE DICIEMBRE</t>
-  </si>
-  <si>
     <t xml:space="preserve">Leonor </t>
   </si>
   <si>
@@ -398,15 +380,9 @@
     <t>Christian / Vanina</t>
   </si>
   <si>
-    <t>4B y Cochera 1 de no cancelar la deuda antes del 10/04 se procedera a desconectar la UF de la luz general de edificio.</t>
-  </si>
-  <si>
     <t>Subidos en ABR 2025</t>
   </si>
   <si>
-    <t>Doartero julio - arreglo de terraza</t>
-  </si>
-  <si>
     <t>Este mes y el anterior lo cerramos sin TSG - EL mes que viene hay que pasar 3</t>
   </si>
   <si>
@@ -419,38 +395,63 @@
     <t>EGRESOS DEL MES DE mayo</t>
   </si>
   <si>
-    <t>Fumigacion mes de abril y mayo</t>
-  </si>
-  <si>
     <t>Vto. 16/06</t>
   </si>
   <si>
-    <t>Matias Salvatierra - Desobstruccion de colectora pluvial</t>
-  </si>
-  <si>
     <t>Matias Salvatierra - Desobstruccion de colectora cloacal</t>
   </si>
   <si>
-    <t>Casa Koruk</t>
+    <t>Fumigacion mes de mayo</t>
+  </si>
+  <si>
+    <t>Casa Koruk - Botas de encargada</t>
+  </si>
+  <si>
+    <t>CAJA ANTERIOR</t>
+  </si>
+  <si>
+    <t>Brian</t>
+  </si>
+  <si>
+    <t>PREVISION EXTRAORDINARIA GASTOS A DEFINIR EN ASAMBLEA</t>
+  </si>
+  <si>
+    <t>Gastos extraordinarios:</t>
+  </si>
+  <si>
+    <t>Expensas ordinarias:</t>
+  </si>
+  <si>
+    <t>ORDINARIAS</t>
+  </si>
+  <si>
+    <t>EXTRAORDINARIAS</t>
+  </si>
+  <si>
+    <t>El 4B abonó parte de la deuda que tiene hasta Octubre de 2024 con la constructora, entendiendo que este mes cancela el resto</t>
+  </si>
+  <si>
+    <t>Seguro de consorcio obligatorio -  federacion patronal - poliza nro. 2027630</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="12">
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+  <numFmts count="13">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="167" formatCode="0.0000"/>
-    <numFmt numFmtId="168" formatCode="&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="169" formatCode="0.0"/>
-    <numFmt numFmtId="170" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
-    <numFmt numFmtId="171" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
-    <numFmt numFmtId="172" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="173" formatCode="_-* #,##0.000000_-;\-* #,##0.000000_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="167" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="168" formatCode="0.0000"/>
+    <numFmt numFmtId="169" formatCode="&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="170" formatCode="0.0"/>
+    <numFmt numFmtId="171" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="172" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="173" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="174" formatCode="_-* #,##0.000000_-;\-* #,##0.000000_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="175" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="32" x14ac:knownFonts="1">
     <font>
@@ -672,7 +673,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -730,6 +731,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1119,11 +1126,11 @@
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="236">
+  <cellXfs count="241">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1131,7 +1138,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1140,27 +1147,27 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1173,8 +1180,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1182,16 +1189,16 @@
     <xf numFmtId="2" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1202,8 +1209,8 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1222,7 +1229,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="19" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
@@ -1233,28 +1240,28 @@
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="18" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="18" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="17" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="18" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="18" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="17" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="21" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="170" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="16" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="16" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1269,13 +1276,13 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="23" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="171" fontId="23" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="23" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1286,24 +1293,24 @@
     <xf numFmtId="43" fontId="26" fillId="5" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="25" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="25" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="25" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="25" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="25" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="5" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="25" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="171" fontId="25" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="25" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="25" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="25" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="25" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="25" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="25" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="25" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="27" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1313,7 +1320,7 @@
     <xf numFmtId="0" fontId="27" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="27" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="27" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1328,19 +1335,19 @@
     <xf numFmtId="0" fontId="27" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="28" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="25" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="28" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="25" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="20" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="25" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="23" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="19" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="172" fontId="25" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="25" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="25" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="23" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="2" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1350,7 +1357,7 @@
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="2" fontId="19" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="19" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1360,9 +1367,9 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="19" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="19" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="19" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="20" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1370,36 +1377,35 @@
     <xf numFmtId="43" fontId="26" fillId="6" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="25" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="28" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="25" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="25" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="25" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="25" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="28" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="25" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="14" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="3" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="25" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="25" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="25" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1409,10 +1415,10 @@
     <xf numFmtId="43" fontId="26" fillId="5" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="25" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="25" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="25" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="25" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="25" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1421,11 +1427,11 @@
     <xf numFmtId="0" fontId="25" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="25" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="6" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="6" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="25" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="25" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="25" fillId="6" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1434,10 +1440,9 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="19" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="10" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="10" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="19" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="19" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="20" fillId="10" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1445,11 +1450,11 @@
     <xf numFmtId="43" fontId="26" fillId="10" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="25" fillId="10" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="10" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="28" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="25" fillId="10" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="25" fillId="10" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="25" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="25" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="28" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="25" fillId="10" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1457,20 +1462,15 @@
     <xf numFmtId="0" fontId="26" fillId="10" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="26" fillId="10" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="4" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="25" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="31" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1484,10 +1484,28 @@
     <xf numFmtId="0" fontId="24" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="171" fontId="31" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="20" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="20" fillId="10" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="9" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1900,17 +1918,17 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F65"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:F64"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>9</v>
       </c>
@@ -1918,460 +1936,446 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="15"/>
       <c r="C5" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>25</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="35" t="s">
         <v>4</v>
       </c>
       <c r="B16" s="28"/>
       <c r="C16" s="36"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="28"/>
       <c r="B17" s="37"/>
       <c r="C17" s="33"/>
       <c r="D17" s="4"/>
       <c r="E17" s="6"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>26</v>
+        <v>134</v>
       </c>
       <c r="B18" s="38"/>
-      <c r="C18" s="222">
+      <c r="C18" s="33">
         <v>41473</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6"/>
     </row>
-    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="28"/>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="28" t="s">
+        <v>10</v>
+      </c>
       <c r="B19" s="39"/>
-      <c r="C19" s="222"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="8"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C19" s="234">
+        <v>307780.02</v>
+      </c>
+      <c r="D19" s="20"/>
+      <c r="F19" s="6"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="B20" s="39"/>
-      <c r="C20" s="223">
-        <v>301604.38</v>
+      <c r="C20" s="33">
+        <v>65000</v>
       </c>
       <c r="D20" s="20"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="39"/>
-      <c r="C21" s="222">
-        <v>65000</v>
-      </c>
-      <c r="D21" s="20"/>
-      <c r="F21" s="6"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="39" t="s">
+      <c r="B21" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="222">
+      <c r="C21" s="33">
         <v>78682.460000000006</v>
       </c>
-      <c r="D22" s="4"/>
-      <c r="E22" s="6"/>
-      <c r="F22" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="40"/>
-      <c r="B23" s="41"/>
-      <c r="C23" s="183">
-        <f>SUM(C17:C22)</f>
-        <v>486759.84</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="35" t="s">
+      <c r="D21" s="4"/>
+      <c r="E21" s="6"/>
+      <c r="F21" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="40"/>
+      <c r="B22" s="41"/>
+      <c r="C22" s="23">
+        <f>SUM(C17:C21)</f>
+        <v>492935.48000000004</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="B24" s="39"/>
-      <c r="C24" s="36"/>
-    </row>
-    <row r="25" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B23" s="39"/>
+      <c r="C23" s="235"/>
+    </row>
+    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="B24" s="42"/>
+      <c r="C24" s="33">
+        <v>349151.87</v>
+      </c>
+      <c r="D24" s="45"/>
+      <c r="F24" s="12"/>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="28" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B25" s="42"/>
-      <c r="C25" s="222">
-        <v>349151.87</v>
+      <c r="C25" s="33">
+        <v>5684</v>
       </c>
       <c r="D25" s="45"/>
       <c r="F25" s="12"/>
     </row>
-    <row r="26" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="28" t="s">
-        <v>121</v>
-      </c>
-      <c r="B26" s="42"/>
-      <c r="C26" s="224">
-        <v>5684</v>
+    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="140" t="s">
+        <v>123</v>
+      </c>
+      <c r="B26" s="141"/>
+      <c r="C26" s="33">
+        <v>56650</v>
       </c>
       <c r="D26" s="45"/>
       <c r="F26" s="12"/>
     </row>
-    <row r="27" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="140" t="s">
+    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="230" t="s">
         <v>125</v>
       </c>
       <c r="B27" s="141"/>
-      <c r="C27" s="222">
-        <v>270000</v>
+      <c r="C27" s="33">
+        <v>20000</v>
       </c>
       <c r="D27" s="45"/>
       <c r="F27" s="12"/>
     </row>
-    <row r="28" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="140" t="s">
-        <v>133</v>
+    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="230" t="s">
+        <v>119</v>
       </c>
       <c r="B28" s="141"/>
-      <c r="C28" s="224">
-        <v>56650</v>
+      <c r="C28" s="33">
+        <v>76654</v>
       </c>
       <c r="D28" s="45"/>
-      <c r="F28" s="12"/>
-    </row>
-    <row r="29" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="140" t="s">
-        <v>132</v>
-      </c>
-      <c r="B29" s="141"/>
-      <c r="C29" s="224">
-        <v>64550</v>
-      </c>
-      <c r="D29" s="45"/>
+      <c r="F28" s="12" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="B29" s="42"/>
+      <c r="C29" s="33">
+        <v>45000</v>
+      </c>
       <c r="F29" s="12"/>
     </row>
-    <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="225" t="s">
-        <v>134</v>
-      </c>
-      <c r="B30" s="141"/>
-      <c r="C30" s="224">
-        <v>20000</v>
-      </c>
-      <c r="D30" s="45"/>
+    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="B30" s="39"/>
+      <c r="C30" s="34"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="6"/>
       <c r="F30" s="12"/>
     </row>
-    <row r="31" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="225" t="s">
-        <v>127</v>
-      </c>
-      <c r="B31" s="141"/>
-      <c r="C31" s="224">
-        <v>76654</v>
-      </c>
-      <c r="D31" s="45"/>
-      <c r="F31" s="12" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="B32" s="42"/>
-      <c r="C32" s="222">
-        <v>45000</v>
+    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="40"/>
+      <c r="B31" s="41"/>
+      <c r="C31" s="23">
+        <f>SUM(C23:C30)</f>
+        <v>553139.87</v>
+      </c>
+      <c r="F31" s="12"/>
+    </row>
+    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="B32" s="30"/>
+      <c r="C32" s="43">
+        <f>+C31+C22</f>
+        <v>1046075.3500000001</v>
       </c>
       <c r="F32" s="12"/>
     </row>
-    <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="28" t="s">
-        <v>113</v>
-      </c>
-      <c r="B33" s="39"/>
-      <c r="C33" s="34"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="6"/>
+    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C33" s="24"/>
       <c r="F33" s="12"/>
     </row>
-    <row r="34" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="40"/>
-      <c r="B34" s="41"/>
-      <c r="C34" s="23">
-        <f>SUM(C24:C33)</f>
-        <v>887689.87</v>
-      </c>
+    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="24"/>
       <c r="F34" s="12"/>
     </row>
-    <row r="35" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="30" t="s">
-        <v>6</v>
-      </c>
-      <c r="B35" s="30"/>
-      <c r="C35" s="43">
-        <f>+C34+C23</f>
-        <v>1374449.71</v>
-      </c>
+    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="28"/>
+      <c r="B35" s="28"/>
+      <c r="C35" s="33"/>
       <c r="F35" s="12"/>
     </row>
-    <row r="36" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C36" s="24"/>
+    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="28"/>
+      <c r="B36" s="28"/>
+      <c r="C36" s="34"/>
       <c r="F36" s="12"/>
     </row>
-    <row r="37" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C37" s="24"/>
+    <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="28"/>
+      <c r="B37" s="28"/>
+      <c r="C37" s="34"/>
       <c r="F37" s="12"/>
     </row>
-    <row r="38" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="28"/>
-      <c r="B38" s="28"/>
-      <c r="C38" s="33"/>
+    <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="236"/>
+      <c r="B38" s="236"/>
+      <c r="C38" s="237"/>
       <c r="F38" s="12"/>
     </row>
-    <row r="39" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="28"/>
-      <c r="B39" s="28"/>
-      <c r="C39" s="34"/>
+    <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="238" t="s">
+        <v>128</v>
+      </c>
+      <c r="B39" s="238"/>
+      <c r="C39" s="239">
+        <v>1000000</v>
+      </c>
       <c r="F39" s="12"/>
     </row>
-    <row r="40" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="28"/>
-      <c r="B40" s="28"/>
-      <c r="C40" s="34"/>
+    <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C40" s="25"/>
       <c r="F40" s="12"/>
     </row>
-    <row r="41" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C41" s="25"/>
-      <c r="F41" s="12"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="13" t="s">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B42" s="13"/>
-      <c r="C42" s="14">
-        <f>+C38+C39+C40+C41</f>
-        <v>0</v>
-      </c>
-      <c r="E42" s="6"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="18" t="s">
+      <c r="B41" s="13"/>
+      <c r="C41" s="14">
+        <f>+C35+C36+C37+C40</f>
+        <v>0</v>
+      </c>
+      <c r="E41" s="6"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B44" s="18"/>
-      <c r="C44" s="19">
-        <f>+C42+C35</f>
-        <v>1374449.71</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B43" s="18"/>
+      <c r="C43" s="19">
+        <f>+C41+C32</f>
+        <v>1046075.3500000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="4"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="4"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C46" s="169"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+    </row>
+    <row r="47" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4"/>
       <c r="C47" s="169"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-    </row>
-    <row r="48" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="4"/>
-      <c r="C48" s="169"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+    </row>
+    <row r="48" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="170" t="s">
+        <v>126</v>
+      </c>
+      <c r="B48" s="168"/>
+      <c r="C48" s="171">
+        <v>-664175.24157355423</v>
+      </c>
       <c r="D48" s="6"/>
       <c r="E48" s="6"/>
     </row>
-    <row r="49" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="170" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B49" s="168"/>
-      <c r="C49" s="171">
-        <v>-108808.68868403265</v>
+      <c r="C49" s="173">
+        <f>-(C32-C30)</f>
+        <v>-1046075.3500000001</v>
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
     </row>
-    <row r="50" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="170" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="B50" s="168"/>
-      <c r="C50" s="173">
-        <f>-(C35-C33)</f>
-        <v>-1374449.71</v>
-      </c>
-      <c r="D50" s="6"/>
-      <c r="E50" s="6"/>
-    </row>
-    <row r="51" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="170" t="s">
-        <v>119</v>
-      </c>
-      <c r="B51" s="168"/>
-      <c r="C51" s="220">
+      <c r="C50" s="218">
         <f>'prorrateo '!F31</f>
-        <v>880779.1571104785</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="174"/>
-      <c r="C52" s="175"/>
-    </row>
-    <row r="53" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="172" t="s">
+        <v>1137720.7895689341</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="174"/>
+      <c r="C51" s="175"/>
+    </row>
+    <row r="52" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="172" t="s">
         <v>8</v>
       </c>
-      <c r="B53" s="167"/>
-      <c r="C53" s="176">
-        <f>SUM(C47:C51)</f>
-        <v>-602479.24157355423</v>
-      </c>
-      <c r="D53" s="5"/>
-    </row>
-    <row r="54" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="9"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="10"/>
-    </row>
-    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="226"/>
-      <c r="B55" s="226"/>
-      <c r="C55" s="226"/>
-      <c r="F55" s="44"/>
-    </row>
-    <row r="56" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="227"/>
-      <c r="B56" s="227"/>
-      <c r="C56" s="227"/>
-    </row>
-    <row r="57" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="26" t="s">
+      <c r="B52" s="167"/>
+      <c r="C52" s="176">
+        <f>SUM(C46:C50)</f>
+        <v>-572529.8020046202</v>
+      </c>
+      <c r="D52" s="5"/>
+    </row>
+    <row r="53" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="9"/>
+      <c r="B53" s="8"/>
+      <c r="C53" s="10"/>
+    </row>
+    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="221"/>
+      <c r="B54" s="221"/>
+      <c r="C54" s="221"/>
+      <c r="F54" s="44"/>
+    </row>
+    <row r="55" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="222"/>
+      <c r="B55" s="222"/>
+      <c r="C55" s="222"/>
+    </row>
+    <row r="56" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="B57" s="27"/>
-      <c r="C57" s="29"/>
-    </row>
-    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="28" t="s">
+      <c r="B56" s="27"/>
+      <c r="C56" s="29"/>
+    </row>
+    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="28" t="s">
         <v>24</v>
       </c>
+      <c r="B57" s="28"/>
+      <c r="C57" s="31">
+        <f>-C41</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="28"/>
       <c r="B58" s="28"/>
-      <c r="C58" s="31">
-        <f>-C42</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C58" s="31"/>
+    </row>
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="28"/>
       <c r="B59" s="28"/>
-      <c r="C59" s="31"/>
-    </row>
-    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="28"/>
-      <c r="B60" s="28"/>
-      <c r="C60" s="32"/>
-    </row>
-    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="177" t="s">
-        <v>0</v>
-      </c>
-      <c r="B61" s="178"/>
-      <c r="C61" s="179">
-        <f>SUM(C57:C60)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C59" s="32"/>
+    </row>
+    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="177" t="s">
+        <v>0</v>
+      </c>
+      <c r="B60" s="178"/>
+      <c r="C60" s="179">
+        <f>SUM(C56:C59)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="8"/>
+      <c r="B61" s="8"/>
+      <c r="C61" s="8"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="8"/>
       <c r="B62" s="8"/>
       <c r="C62" s="8"/>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="8"/>
       <c r="B63" s="8"/>
       <c r="C63" s="8"/>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="8"/>
       <c r="B64" s="8"/>
       <c r="C64" s="8"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="8"/>
-      <c r="B65" s="8"/>
-      <c r="C65" s="8"/>
-    </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A55:C56"/>
+    <mergeCell ref="A54:C55"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -2389,94 +2393,101 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.88671875" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.88671875" customWidth="1"/>
-    <col min="9" max="9" width="10.6640625" customWidth="1"/>
-    <col min="10" max="10" width="10.5546875" customWidth="1"/>
-    <col min="11" max="11" width="0.109375" customWidth="1"/>
-    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.44140625" style="11"/>
+    <col min="1" max="1" width="19.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" customWidth="1"/>
+    <col min="9" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" customWidth="1"/>
+    <col min="11" max="11" width="0.140625" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.42578125" style="11"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B1" s="228">
+        <v>130</v>
+      </c>
+      <c r="B1" s="223">
         <f>D1</f>
         <v>1436145.71</v>
       </c>
-      <c r="C1" s="228"/>
+      <c r="C1" s="223"/>
       <c r="D1" s="145">
         <v>1436145.71</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G1" s="240">
+        <v>1000000</v>
+      </c>
+      <c r="H1" s="240"/>
+    </row>
+    <row r="2" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="46" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B2" s="46" t="s">
         <v>20</v>
       </c>
       <c r="C2" s="139" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D2" s="47" t="s">
         <v>1</v>
       </c>
       <c r="E2" s="48" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="48" t="s">
+      <c r="G2" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="49" t="s">
-        <v>31</v>
-      </c>
       <c r="H2" s="49" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="I2" s="50" t="s">
-        <v>32</v>
+        <v>131</v>
       </c>
       <c r="J2" s="50" t="s">
-        <v>33</v>
+        <v>132</v>
       </c>
       <c r="K2" s="50" t="s">
         <v>17</v>
       </c>
       <c r="L2" s="51" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B3" s="53" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C3" s="54" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D3" s="55">
         <v>5.1100000000000003</v>
       </c>
       <c r="E3" s="131">
-        <v>45994.165161000004</v>
-      </c>
-      <c r="F3" s="196">
+        <v>73387.045781000008</v>
+      </c>
+      <c r="F3" s="231">
         <f>E3</f>
-        <v>45994.165161000004</v>
+        <v>73387.045781000008</v>
       </c>
       <c r="G3" s="56">
         <f>E3-F3</f>
@@ -2491,33 +2502,34 @@
         <v>73387.045781000008</v>
       </c>
       <c r="J3" s="56">
-        <v>0</v>
+        <f>G$1*D3/100</f>
+        <v>51100</v>
       </c>
       <c r="K3" s="56"/>
       <c r="L3" s="57">
         <f>I3+G3+K3+J3+H3</f>
-        <v>73387.045781000008</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+        <v>124487.04578100001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="58" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B4" s="59" t="s">
-        <v>38</v>
+        <v>127</v>
       </c>
       <c r="C4" s="60" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D4" s="61">
         <v>5.09</v>
       </c>
       <c r="E4" s="131">
-        <v>45814.148859000001</v>
-      </c>
-      <c r="F4" s="196">
+        <v>73099.816638999997</v>
+      </c>
+      <c r="F4" s="231">
         <f t="shared" ref="F4:F23" si="0">E4</f>
-        <v>45814.148859000001</v>
+        <v>73099.816638999997</v>
       </c>
       <c r="G4" s="56">
         <f t="shared" ref="G4:G29" si="1">E4-F4</f>
@@ -2532,72 +2544,71 @@
         <v>73099.816638999997</v>
       </c>
       <c r="J4" s="56">
-        <v>0</v>
+        <f t="shared" ref="J4:J29" si="4">G$1*D4/100</f>
+        <v>50900</v>
       </c>
       <c r="K4" s="56"/>
       <c r="L4" s="57">
-        <f t="shared" ref="L4:L29" si="4">I4+G4+K4+J4+H4</f>
-        <v>73099.816638999997</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+        <f t="shared" ref="L4:L29" si="5">I4+G4+K4+J4+H4</f>
+        <v>123999.816639</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B5" s="59" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C5" s="60" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D5" s="61">
         <v>5.04</v>
       </c>
       <c r="E5" s="131">
-        <v>45364.108103999999</v>
-      </c>
-      <c r="F5" s="196">
-        <f t="shared" si="0"/>
-        <v>45364.108103999999</v>
-      </c>
+        <v>72381.743783999991</v>
+      </c>
+      <c r="F5" s="231"/>
       <c r="G5" s="56">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>72381.743783999991</v>
       </c>
       <c r="H5" s="56">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2895.2697513599996</v>
       </c>
       <c r="I5" s="56">
         <f t="shared" si="3"/>
         <v>72381.743783999991</v>
       </c>
       <c r="J5" s="56">
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>50400</v>
       </c>
       <c r="K5" s="56"/>
       <c r="L5" s="57">
-        <f t="shared" si="4"/>
-        <v>72381.743783999991</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+        <f t="shared" si="5"/>
+        <v>198058.75731935998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="58" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B6" s="59"/>
       <c r="C6" s="60" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D6" s="61">
         <v>5.21</v>
       </c>
       <c r="E6" s="131">
-        <v>46894.246671000001</v>
-      </c>
-      <c r="F6" s="196">
+        <v>74823.191491000005</v>
+      </c>
+      <c r="F6" s="231">
         <f>E6</f>
-        <v>46894.246671000001</v>
+        <v>74823.191491000005</v>
       </c>
       <c r="G6" s="56">
         <f t="shared" si="1"/>
@@ -2612,72 +2623,71 @@
         <v>74823.191491000005</v>
       </c>
       <c r="J6" s="56">
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>52100</v>
       </c>
       <c r="K6" s="56"/>
       <c r="L6" s="57">
-        <f t="shared" si="4"/>
-        <v>74823.191491000005</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+        <f t="shared" si="5"/>
+        <v>126923.19149100001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B7" s="59" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C7" s="60" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D7" s="61">
         <v>5.1100000000000003</v>
       </c>
       <c r="E7" s="131">
-        <v>45994.165161000004</v>
-      </c>
-      <c r="F7" s="196">
-        <f>E7</f>
-        <v>45994.165161000004</v>
-      </c>
+        <v>73387.045781000008</v>
+      </c>
+      <c r="F7" s="231"/>
       <c r="G7" s="56">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>73387.045781000008</v>
       </c>
       <c r="H7" s="56">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2935.4818312400002</v>
       </c>
       <c r="I7" s="56">
         <f t="shared" si="3"/>
         <v>73387.045781000008</v>
       </c>
       <c r="J7" s="56">
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>51100</v>
       </c>
       <c r="K7" s="56"/>
       <c r="L7" s="57">
-        <f t="shared" si="4"/>
-        <v>73387.045781000008</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+        <f t="shared" si="5"/>
+        <v>200809.57339324002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="58" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B8" s="59"/>
       <c r="C8" s="60" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D8" s="61">
         <v>5.09</v>
       </c>
       <c r="E8" s="131">
-        <v>45814.148859000001</v>
-      </c>
-      <c r="F8" s="196">
+        <v>73099.816638999997</v>
+      </c>
+      <c r="F8" s="231">
         <f>E8</f>
-        <v>45814.148859000001</v>
+        <v>73099.816638999997</v>
       </c>
       <c r="G8" s="56">
         <f t="shared" si="1"/>
@@ -2692,31 +2702,32 @@
         <v>73099.816638999997</v>
       </c>
       <c r="J8" s="56">
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>50900</v>
       </c>
       <c r="K8" s="56"/>
       <c r="L8" s="57">
-        <f t="shared" si="4"/>
-        <v>73099.816638999997</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+        <f t="shared" si="5"/>
+        <v>123999.816639</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B9" s="59"/>
       <c r="C9" s="60" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D9" s="61">
         <v>5.1100000000000003</v>
       </c>
       <c r="E9" s="131">
-        <v>45994.165161000004</v>
-      </c>
-      <c r="F9" s="196">
+        <v>73387.045781000008</v>
+      </c>
+      <c r="F9" s="231">
         <f t="shared" si="0"/>
-        <v>45994.165161000004</v>
+        <v>73387.045781000008</v>
       </c>
       <c r="G9" s="56">
         <f t="shared" si="1"/>
@@ -2731,69 +2742,71 @@
         <v>73387.045781000008</v>
       </c>
       <c r="J9" s="56">
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>51100</v>
       </c>
       <c r="K9" s="56"/>
       <c r="L9" s="57">
-        <f t="shared" si="4"/>
-        <v>73387.045781000008</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="198" t="s">
-        <v>50</v>
-      </c>
-      <c r="B10" s="199" t="s">
-        <v>122</v>
-      </c>
-      <c r="C10" s="200" t="s">
-        <v>51</v>
-      </c>
-      <c r="D10" s="201">
+        <f t="shared" si="5"/>
+        <v>124487.04578100001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="233" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="198" t="s">
+        <v>116</v>
+      </c>
+      <c r="C10" s="199" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="200">
         <v>5.09</v>
       </c>
-      <c r="E10" s="202">
-        <v>257006.18515366298</v>
-      </c>
-      <c r="F10" s="203"/>
-      <c r="G10" s="204">
+      <c r="E10" s="201">
+        <v>340386.24919880956</v>
+      </c>
+      <c r="F10" s="232"/>
+      <c r="G10" s="202">
         <f t="shared" si="1"/>
-        <v>257006.18515366298</v>
-      </c>
-      <c r="H10" s="204">
+        <v>340386.24919880956</v>
+      </c>
+      <c r="H10" s="202">
         <f t="shared" si="2"/>
-        <v>10280.24740614652</v>
-      </c>
-      <c r="I10" s="204">
+        <v>13615.449967952383</v>
+      </c>
+      <c r="I10" s="202">
         <f t="shared" si="3"/>
         <v>73099.816638999997</v>
       </c>
-      <c r="J10" s="204">
-        <v>0</v>
-      </c>
-      <c r="K10" s="204"/>
-      <c r="L10" s="205">
+      <c r="J10" s="202">
         <f t="shared" si="4"/>
-        <v>340386.24919880956</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+        <v>50900</v>
+      </c>
+      <c r="K10" s="202"/>
+      <c r="L10" s="203">
+        <f t="shared" si="5"/>
+        <v>478001.51580576197</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B11" s="59"/>
       <c r="C11" s="60" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D11" s="61">
         <v>5.04</v>
       </c>
       <c r="E11" s="131">
-        <v>45364.108103999999</v>
-      </c>
-      <c r="F11" s="196">
+        <v>72381.743783999991</v>
+      </c>
+      <c r="F11" s="231">
         <f>E11</f>
-        <v>45364.108103999999</v>
+        <v>72381.743783999991</v>
       </c>
       <c r="G11" s="56">
         <f t="shared" si="1"/>
@@ -2808,31 +2821,32 @@
         <v>72381.743783999991</v>
       </c>
       <c r="J11" s="56">
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>50400</v>
       </c>
       <c r="K11" s="56"/>
       <c r="L11" s="57">
-        <f t="shared" si="4"/>
-        <v>72381.743783999991</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+        <f t="shared" si="5"/>
+        <v>122781.74378399999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="58" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B12" s="59"/>
       <c r="C12" s="60" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D12" s="61">
         <v>5.21</v>
       </c>
       <c r="E12" s="131">
-        <v>46894.246671000001</v>
-      </c>
-      <c r="F12" s="196">
+        <v>74823.191491000005</v>
+      </c>
+      <c r="F12" s="231">
         <f t="shared" si="0"/>
-        <v>46894.246671000001</v>
+        <v>74823.191491000005</v>
       </c>
       <c r="G12" s="56">
         <f t="shared" si="1"/>
@@ -2847,33 +2861,34 @@
         <v>74823.191491000005</v>
       </c>
       <c r="J12" s="56">
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>52100</v>
       </c>
       <c r="K12" s="56"/>
       <c r="L12" s="57">
-        <f t="shared" si="4"/>
-        <v>74823.191491000005</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+        <f t="shared" si="5"/>
+        <v>126923.19149100001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B13" s="59" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C13" s="60" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D13" s="61">
         <v>5.1100000000000003</v>
       </c>
       <c r="E13" s="131">
-        <v>45994.165161000004</v>
-      </c>
-      <c r="F13" s="196">
+        <v>73387.045781000008</v>
+      </c>
+      <c r="F13" s="231">
         <f>E13</f>
-        <v>45994.165161000004</v>
+        <v>73387.045781000008</v>
       </c>
       <c r="G13" s="56">
         <f t="shared" si="1"/>
@@ -2888,149 +2903,150 @@
         <v>73387.045781000008</v>
       </c>
       <c r="J13" s="56">
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>51100</v>
       </c>
       <c r="K13" s="56"/>
       <c r="L13" s="57">
-        <f t="shared" si="4"/>
-        <v>73387.045781000008</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+        <f t="shared" si="5"/>
+        <v>124487.04578100001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="64" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B14" s="142"/>
       <c r="C14" s="65" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D14" s="143">
         <v>5.09</v>
       </c>
       <c r="E14" s="131">
-        <v>137780.54635439839</v>
-      </c>
-      <c r="F14" s="196">
-        <f>E14</f>
-        <v>137780.54635439839</v>
-      </c>
+        <v>73099.816638999997</v>
+      </c>
+      <c r="F14" s="231"/>
       <c r="G14" s="66">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>73099.816638999997</v>
       </c>
       <c r="H14" s="66">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2923.9926655599998</v>
       </c>
       <c r="I14" s="66">
         <f t="shared" si="3"/>
         <v>73099.816638999997</v>
       </c>
-      <c r="J14" s="66">
-        <v>0</v>
+      <c r="J14" s="56">
+        <f t="shared" si="4"/>
+        <v>50900</v>
       </c>
       <c r="K14" s="66"/>
       <c r="L14" s="144">
-        <f t="shared" si="4"/>
-        <v>73099.816638999997</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+        <f t="shared" si="5"/>
+        <v>200023.62594356001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B15" s="59" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C15" s="60" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D15" s="61">
         <v>5.04</v>
       </c>
       <c r="E15" s="131">
-        <v>136427.10287351039</v>
-      </c>
-      <c r="F15" s="196"/>
+        <v>214265.93077245081</v>
+      </c>
+      <c r="F15" s="231">
+        <f>E15</f>
+        <v>214265.93077245081</v>
+      </c>
       <c r="G15" s="56">
         <f t="shared" si="1"/>
-        <v>136427.10287351039</v>
+        <v>0</v>
       </c>
       <c r="H15" s="56">
         <f t="shared" si="2"/>
-        <v>5457.0841149404159</v>
+        <v>0</v>
       </c>
       <c r="I15" s="56">
         <f t="shared" si="3"/>
         <v>72381.743783999991</v>
       </c>
       <c r="J15" s="56">
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>50400</v>
       </c>
       <c r="K15" s="56"/>
       <c r="L15" s="57">
-        <f t="shared" si="4"/>
-        <v>214265.93077245081</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+        <f t="shared" si="5"/>
+        <v>122781.74378399999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="58" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B16" s="59" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C16" s="60" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D16" s="61">
         <v>5.21</v>
       </c>
       <c r="E16" s="131">
-        <v>46894.246671000001</v>
-      </c>
-      <c r="F16" s="196">
-        <f>E16</f>
-        <v>46894.246671000001</v>
-      </c>
+        <v>74823.191491000005</v>
+      </c>
+      <c r="F16" s="231"/>
       <c r="G16" s="56">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>74823.191491000005</v>
       </c>
       <c r="H16" s="56">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2992.9276596400005</v>
       </c>
       <c r="I16" s="56">
         <f t="shared" si="3"/>
         <v>74823.191491000005</v>
       </c>
       <c r="J16" s="56">
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>52100</v>
       </c>
       <c r="K16" s="56"/>
       <c r="L16" s="57">
-        <f t="shared" si="4"/>
-        <v>74823.191491000005</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+        <f t="shared" si="5"/>
+        <v>204739.31064164001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B17" s="59"/>
       <c r="C17" s="60" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D17" s="61">
         <v>5.04</v>
       </c>
       <c r="E17" s="131">
-        <v>45364.108103999999</v>
-      </c>
-      <c r="F17" s="196">
+        <v>72381.743783999991</v>
+      </c>
+      <c r="F17" s="231">
         <f t="shared" si="0"/>
-        <v>45364.108103999999</v>
+        <v>72381.743783999991</v>
       </c>
       <c r="G17" s="56">
         <f t="shared" si="1"/>
@@ -3045,31 +3061,32 @@
         <v>72381.743783999991</v>
       </c>
       <c r="J17" s="56">
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>50400</v>
       </c>
       <c r="K17" s="56"/>
       <c r="L17" s="57">
-        <f t="shared" si="4"/>
-        <v>72381.743783999991</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="5"/>
+        <v>122781.74378399999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="62" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B18" s="63"/>
       <c r="C18" s="60" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D18" s="61">
         <v>5.21</v>
       </c>
       <c r="E18" s="131">
-        <v>46894.246671000001</v>
-      </c>
-      <c r="F18" s="196">
+        <v>74823.191491000005</v>
+      </c>
+      <c r="F18" s="231">
         <f t="shared" si="0"/>
-        <v>46894.246671000001</v>
+        <v>74823.191491000005</v>
       </c>
       <c r="G18" s="56">
         <f t="shared" si="1"/>
@@ -3084,31 +3101,32 @@
         <v>74823.191491000005</v>
       </c>
       <c r="J18" s="56">
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>52100</v>
       </c>
       <c r="K18" s="56"/>
       <c r="L18" s="57">
-        <f t="shared" si="4"/>
-        <v>74823.191491000005</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+        <f t="shared" si="5"/>
+        <v>126923.19149100001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B19" s="59"/>
       <c r="C19" s="60" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D19" s="61">
         <v>7.4</v>
       </c>
       <c r="E19" s="131">
-        <v>66606.031740000006</v>
-      </c>
-      <c r="F19" s="196">
+        <v>106274.78254</v>
+      </c>
+      <c r="F19" s="231">
         <f>E19</f>
-        <v>66606.031740000006</v>
+        <v>106274.78254</v>
       </c>
       <c r="G19" s="56">
         <f t="shared" si="1"/>
@@ -3123,185 +3141,184 @@
         <v>106274.78254</v>
       </c>
       <c r="J19" s="56">
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>74000</v>
       </c>
       <c r="K19" s="56"/>
       <c r="L19" s="57">
-        <f t="shared" si="4"/>
-        <v>106274.78254</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="24" x14ac:dyDescent="0.3">
-      <c r="A20" s="198"/>
-      <c r="B20" s="199" t="s">
-        <v>122</v>
-      </c>
-      <c r="C20" s="200" t="s">
-        <v>71</v>
-      </c>
-      <c r="D20" s="201">
+        <f t="shared" si="5"/>
+        <v>180274.78253999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="24" x14ac:dyDescent="0.25">
+      <c r="A20" s="197"/>
+      <c r="B20" s="198" t="s">
+        <v>116</v>
+      </c>
+      <c r="C20" s="199" t="s">
+        <v>67</v>
+      </c>
+      <c r="D20" s="200">
         <v>1.08</v>
       </c>
-      <c r="E20" s="202">
-        <v>54531.764236926552</v>
-      </c>
-      <c r="F20" s="203">
-        <v>0</v>
-      </c>
-      <c r="G20" s="204">
+      <c r="E20" s="201">
+        <v>72223.408474403608</v>
+      </c>
+      <c r="F20" s="232">
+        <v>0</v>
+      </c>
+      <c r="G20" s="202">
         <f t="shared" si="1"/>
-        <v>54531.764236926552</v>
-      </c>
-      <c r="H20" s="204">
+        <v>72223.408474403608</v>
+      </c>
+      <c r="H20" s="202">
         <f t="shared" si="2"/>
-        <v>2181.2705694770621</v>
-      </c>
-      <c r="I20" s="204">
+        <v>2888.9363389761443</v>
+      </c>
+      <c r="I20" s="202">
         <f t="shared" si="3"/>
         <v>15510.373668</v>
       </c>
-      <c r="J20" s="204">
-        <v>0</v>
-      </c>
-      <c r="K20" s="204"/>
-      <c r="L20" s="205">
+      <c r="J20" s="202">
         <f t="shared" si="4"/>
-        <v>72223.408474403608</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+        <v>10800</v>
+      </c>
+      <c r="K20" s="202"/>
+      <c r="L20" s="203">
+        <f t="shared" si="5"/>
+        <v>101422.71848137975</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="64"/>
       <c r="B21" s="59" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C21" s="65" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D21" s="61">
         <v>1.08</v>
       </c>
       <c r="E21" s="131">
-        <v>9720.8803079999998</v>
-      </c>
-      <c r="F21" s="196">
-        <f>E21</f>
-        <v>9720.8803079999998</v>
-      </c>
+        <v>15510.373668</v>
+      </c>
+      <c r="F21" s="195"/>
       <c r="G21" s="56">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>15510.373668</v>
       </c>
       <c r="H21" s="56">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>620.41494671999999</v>
       </c>
       <c r="I21" s="56">
         <f t="shared" si="3"/>
         <v>15510.373668</v>
       </c>
       <c r="J21" s="56">
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>10800</v>
       </c>
       <c r="K21" s="66"/>
       <c r="L21" s="57">
-        <f t="shared" si="4"/>
-        <v>15510.373668</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+        <f t="shared" si="5"/>
+        <v>42441.162282719997</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="146"/>
       <c r="B22" s="147"/>
       <c r="C22" s="148" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D22" s="149">
         <v>1.08</v>
       </c>
       <c r="E22" s="150">
-        <v>54531.764236926552</v>
-      </c>
-      <c r="F22" s="197">
+        <v>72223.408474403608</v>
+      </c>
+      <c r="F22" s="196">
         <v>0</v>
       </c>
       <c r="G22" s="151">
         <f t="shared" si="1"/>
-        <v>54531.764236926552</v>
+        <v>72223.408474403608</v>
       </c>
       <c r="H22" s="151">
         <f t="shared" si="2"/>
-        <v>2181.2705694770621</v>
+        <v>2888.9363389761443</v>
       </c>
       <c r="I22" s="151">
         <f t="shared" si="3"/>
         <v>15510.373668</v>
       </c>
       <c r="J22" s="151">
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>10800</v>
       </c>
       <c r="K22" s="151"/>
       <c r="L22" s="152">
-        <f t="shared" si="4"/>
-        <v>72223.408474403608</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+        <f t="shared" si="5"/>
+        <v>101422.71848137975</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="58"/>
       <c r="B23" s="59" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C23" s="60" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D23" s="61">
         <v>1.08</v>
       </c>
       <c r="E23" s="131">
-        <v>9720.8803079999998</v>
-      </c>
-      <c r="F23" s="196">
-        <f t="shared" si="0"/>
-        <v>9720.8803079999998</v>
-      </c>
+        <v>15510.373668</v>
+      </c>
+      <c r="F23" s="195"/>
       <c r="G23" s="56">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>15510.373668</v>
       </c>
       <c r="H23" s="56">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>620.41494671999999</v>
       </c>
       <c r="I23" s="56">
         <f t="shared" si="3"/>
         <v>15510.373668</v>
       </c>
       <c r="J23" s="56">
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>10800</v>
       </c>
       <c r="K23" s="56"/>
       <c r="L23" s="57">
-        <f t="shared" si="4"/>
-        <v>15510.373668</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+        <f t="shared" si="5"/>
+        <v>42441.162282719997</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="58" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B24" s="59" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C24" s="60" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D24" s="61">
         <v>1.08</v>
       </c>
       <c r="E24" s="131">
-        <v>9720.8803079999998</v>
-      </c>
-      <c r="F24" s="196">
+        <v>15510.373668</v>
+      </c>
+      <c r="F24" s="231">
         <f>E24</f>
-        <v>9720.8803079999998</v>
+        <v>15510.373668</v>
       </c>
       <c r="G24" s="56">
         <f t="shared" si="1"/>
@@ -3316,70 +3333,69 @@
         <v>15510.373668</v>
       </c>
       <c r="J24" s="56">
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>10800</v>
       </c>
       <c r="K24" s="56"/>
       <c r="L24" s="57">
-        <f t="shared" si="4"/>
-        <v>15510.373668</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+        <f t="shared" si="5"/>
+        <v>26310.373668</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B25" s="59"/>
       <c r="C25" s="60" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D25" s="61">
         <v>1.08</v>
       </c>
       <c r="E25" s="131">
-        <v>18793.027810079999</v>
-      </c>
-      <c r="F25" s="196">
-        <f>E25</f>
-        <v>18793.027810079999</v>
-      </c>
+        <v>15510.373668</v>
+      </c>
+      <c r="F25" s="231"/>
       <c r="G25" s="56">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>15510.373668</v>
       </c>
       <c r="H25" s="56">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>620.41494671999999</v>
       </c>
       <c r="I25" s="56">
         <f t="shared" si="3"/>
         <v>15510.373668</v>
       </c>
       <c r="J25" s="56">
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>10800</v>
       </c>
       <c r="K25" s="56"/>
       <c r="L25" s="57">
-        <f t="shared" si="4"/>
-        <v>15510.373668</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+        <f t="shared" si="5"/>
+        <v>42441.162282719997</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="58" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B26" s="59"/>
       <c r="C26" s="60" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D26" s="61">
         <v>1.08</v>
       </c>
       <c r="E26" s="131">
-        <v>9720.8803079999998</v>
-      </c>
-      <c r="F26" s="196">
-        <f t="shared" ref="F26:F28" si="5">E26</f>
-        <v>9720.8803079999998</v>
+        <v>15510.373668</v>
+      </c>
+      <c r="F26" s="231">
+        <f t="shared" ref="F26:F28" si="6">E26</f>
+        <v>15510.373668</v>
       </c>
       <c r="G26" s="56">
         <f t="shared" si="1"/>
@@ -3394,31 +3410,32 @@
         <v>15510.373668</v>
       </c>
       <c r="J26" s="56">
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>10800</v>
       </c>
       <c r="K26" s="56"/>
       <c r="L26" s="57">
-        <f t="shared" si="4"/>
-        <v>15510.373668</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+        <f t="shared" si="5"/>
+        <v>26310.373668</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="58" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B27" s="67"/>
       <c r="C27" s="60" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D27" s="61">
         <v>1.08</v>
       </c>
       <c r="E27" s="131">
-        <v>9720.8803079999998</v>
-      </c>
-      <c r="F27" s="196">
-        <f t="shared" si="5"/>
-        <v>9720.8803079999998</v>
+        <v>15510.373668</v>
+      </c>
+      <c r="F27" s="231">
+        <f t="shared" si="6"/>
+        <v>15510.373668</v>
       </c>
       <c r="G27" s="56">
         <f t="shared" si="1"/>
@@ -3433,95 +3450,100 @@
         <v>15510.373668</v>
       </c>
       <c r="J27" s="56">
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>10800</v>
       </c>
       <c r="K27" s="56"/>
       <c r="L27" s="57">
-        <f t="shared" si="4"/>
-        <v>15510.373668</v>
+        <f t="shared" si="5"/>
+        <v>26310.373668</v>
       </c>
       <c r="O27" s="44">
         <f>F27+F26+F19</f>
-        <v>86047.792356000005</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+        <v>137295.52987600002</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="68"/>
       <c r="B28" s="67" t="str">
         <f>B7</f>
         <v>Leandro</v>
       </c>
       <c r="C28" s="60" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D28" s="61">
         <v>1.08</v>
       </c>
       <c r="E28" s="131">
-        <v>9720.8803079999998</v>
-      </c>
-      <c r="F28" s="196">
-        <f t="shared" si="5"/>
-        <v>9720.8803079999998</v>
-      </c>
+        <v>15510.373668</v>
+      </c>
+      <c r="F28" s="231"/>
       <c r="G28" s="56">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>15510.373668</v>
       </c>
       <c r="H28" s="56">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>620.41494671999999</v>
       </c>
       <c r="I28" s="56">
         <f t="shared" si="3"/>
         <v>15510.373668</v>
       </c>
       <c r="J28" s="56">
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>10800</v>
       </c>
       <c r="K28" s="56"/>
       <c r="L28" s="57">
-        <f t="shared" si="4"/>
-        <v>15510.373668</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+        <f t="shared" si="5"/>
+        <v>42441.162282719997</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="68" t="s">
-        <v>59</v>
-      </c>
-      <c r="B29" s="67"/>
+        <v>55</v>
+      </c>
+      <c r="B29" s="59" t="s">
+        <v>56</v>
+      </c>
       <c r="C29" s="60" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D29" s="61">
         <v>1.08</v>
       </c>
       <c r="E29" s="131">
-        <v>18793.027810079999</v>
-      </c>
-      <c r="F29" s="196"/>
+        <v>35055.122590483195</v>
+      </c>
+      <c r="F29" s="231">
+        <f>E29</f>
+        <v>35055.122590483195</v>
+      </c>
       <c r="G29" s="56">
         <f t="shared" si="1"/>
-        <v>18793.027810079999</v>
+        <v>0</v>
       </c>
       <c r="H29" s="56">
         <f t="shared" si="2"/>
-        <v>751.72111240319998</v>
+        <v>0</v>
       </c>
       <c r="I29" s="56">
         <f t="shared" si="3"/>
         <v>15510.373668</v>
       </c>
       <c r="J29" s="56">
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>10800</v>
       </c>
       <c r="K29" s="56"/>
       <c r="L29" s="57">
-        <f t="shared" si="4"/>
-        <v>35055.122590483195</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+        <f t="shared" si="5"/>
+        <v>26310.373668</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="69"/>
       <c r="B30" s="69"/>
       <c r="C30" s="70"/>
@@ -3535,11 +3557,11 @@
       <c r="K30" s="73"/>
       <c r="L30" s="73"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="74"/>
       <c r="B31" s="75"/>
       <c r="C31" s="76" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D31" s="76">
         <f>SUM(D3:D30)</f>
@@ -3548,7 +3570,7 @@
       <c r="E31" s="75"/>
       <c r="F31" s="137">
         <f>SUM(F3:F30)</f>
-        <v>880779.1571104785</v>
+        <v>1137720.7895689341</v>
       </c>
       <c r="G31" s="77"/>
       <c r="H31" s="77"/>
@@ -3556,84 +3578,85 @@
         <f>SUM(I3:I30)</f>
         <v>1436145.7100000009</v>
       </c>
-      <c r="J31" s="137">
+      <c r="J31" s="138">
         <f>SUM(J3:J30)</f>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="K31" s="137"/>
       <c r="L31" s="137">
         <f>SUM(L3:L29)</f>
-        <v>1978287.1480835518</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+        <v>3310334.7228552024</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="J32" s="22"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" s="229" t="s">
-        <v>123</v>
-      </c>
-      <c r="B33" s="229"/>
-      <c r="C33" s="229"/>
-      <c r="D33" s="229"/>
-      <c r="E33" s="229"/>
-      <c r="F33" s="229"/>
-      <c r="G33" s="229"/>
-      <c r="H33" s="229"/>
-      <c r="I33" s="229"/>
-      <c r="J33" s="229"/>
-      <c r="K33" s="229"/>
-      <c r="L33" s="229"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" s="229"/>
-      <c r="B34" s="229"/>
-      <c r="C34" s="229"/>
-      <c r="D34" s="229"/>
-      <c r="E34" s="229"/>
-      <c r="F34" s="229"/>
-      <c r="G34" s="229"/>
-      <c r="H34" s="229"/>
-      <c r="I34" s="229"/>
-      <c r="J34" s="229"/>
-      <c r="K34" s="229"/>
-      <c r="L34" s="229"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" s="229"/>
-      <c r="B35" s="229"/>
-      <c r="C35" s="229"/>
-      <c r="D35" s="229"/>
-      <c r="E35" s="229"/>
-      <c r="F35" s="229"/>
-      <c r="G35" s="229"/>
-      <c r="H35" s="229"/>
-      <c r="I35" s="229"/>
-      <c r="J35" s="229"/>
-      <c r="K35" s="229"/>
-      <c r="L35" s="229"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="229"/>
-      <c r="B36" s="229"/>
-      <c r="C36" s="229"/>
-      <c r="D36" s="229"/>
-      <c r="E36" s="229"/>
-      <c r="F36" s="229"/>
-      <c r="G36" s="229"/>
-      <c r="H36" s="229"/>
-      <c r="I36" s="229"/>
-      <c r="J36" s="229"/>
-      <c r="K36" s="229"/>
-      <c r="L36" s="229"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="224" t="s">
+        <v>133</v>
+      </c>
+      <c r="B33" s="224"/>
+      <c r="C33" s="224"/>
+      <c r="D33" s="224"/>
+      <c r="E33" s="224"/>
+      <c r="F33" s="224"/>
+      <c r="G33" s="224"/>
+      <c r="H33" s="224"/>
+      <c r="I33" s="224"/>
+      <c r="J33" s="224"/>
+      <c r="K33" s="224"/>
+      <c r="L33" s="224"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" s="224"/>
+      <c r="B34" s="224"/>
+      <c r="C34" s="224"/>
+      <c r="D34" s="224"/>
+      <c r="E34" s="224"/>
+      <c r="F34" s="224"/>
+      <c r="G34" s="224"/>
+      <c r="H34" s="224"/>
+      <c r="I34" s="224"/>
+      <c r="J34" s="224"/>
+      <c r="K34" s="224"/>
+      <c r="L34" s="224"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" s="224"/>
+      <c r="B35" s="224"/>
+      <c r="C35" s="224"/>
+      <c r="D35" s="224"/>
+      <c r="E35" s="224"/>
+      <c r="F35" s="224"/>
+      <c r="G35" s="224"/>
+      <c r="H35" s="224"/>
+      <c r="I35" s="224"/>
+      <c r="J35" s="224"/>
+      <c r="K35" s="224"/>
+      <c r="L35" s="224"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" s="224"/>
+      <c r="B36" s="224"/>
+      <c r="C36" s="224"/>
+      <c r="D36" s="224"/>
+      <c r="E36" s="224"/>
+      <c r="F36" s="224"/>
+      <c r="G36" s="224"/>
+      <c r="H36" s="224"/>
+      <c r="I36" s="224"/>
+      <c r="J36" s="224"/>
+      <c r="K36" s="224"/>
+      <c r="L36" s="224"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E40" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="A33:L36"/>
+    <mergeCell ref="G1:H1"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -3644,167 +3667,167 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:S46"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="8.33203125" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="15.109375" customWidth="1"/>
-    <col min="4" max="4" width="15.109375" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="8.28515625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="9" customWidth="1"/>
-    <col min="6" max="6" width="9.33203125" customWidth="1"/>
-    <col min="7" max="7" width="9.5546875" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="0.109375" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="13.88671875" customWidth="1"/>
-    <col min="11" max="11" width="0.109375" customWidth="1"/>
-    <col min="12" max="12" width="13.5546875" customWidth="1"/>
-    <col min="13" max="13" width="11.88671875" customWidth="1"/>
-    <col min="14" max="14" width="12.88671875" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="9.28515625" customWidth="1"/>
+    <col min="7" max="7" width="9.5703125" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="0.140625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="13.85546875" customWidth="1"/>
+    <col min="11" max="11" width="0.140625" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" customWidth="1"/>
+    <col min="13" max="13" width="11.85546875" customWidth="1"/>
+    <col min="14" max="14" width="12.85546875" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="230" t="s">
-        <v>84</v>
-      </c>
-      <c r="B1" s="231"/>
-      <c r="C1" s="231"/>
-      <c r="D1" s="231"/>
-      <c r="E1" s="231"/>
-      <c r="F1" s="231"/>
-      <c r="G1" s="231"/>
-      <c r="H1" s="231"/>
-      <c r="I1" s="231"/>
-      <c r="J1" s="231"/>
-      <c r="K1" s="231"/>
-      <c r="L1" s="231"/>
-      <c r="M1" s="231"/>
-      <c r="N1" s="232"/>
+    <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="225" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="226"/>
+      <c r="C1" s="226"/>
+      <c r="D1" s="226"/>
+      <c r="E1" s="226"/>
+      <c r="F1" s="226"/>
+      <c r="G1" s="226"/>
+      <c r="H1" s="226"/>
+      <c r="I1" s="226"/>
+      <c r="J1" s="226"/>
+      <c r="K1" s="226"/>
+      <c r="L1" s="226"/>
+      <c r="M1" s="226"/>
+      <c r="N1" s="227"/>
       <c r="O1" s="78"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="79"/>
       <c r="B2" s="79"/>
-      <c r="C2" s="184"/>
-      <c r="D2" s="184"/>
-      <c r="E2" s="184"/>
-      <c r="F2" s="184"/>
-      <c r="G2" s="184"/>
-      <c r="H2" s="185"/>
-      <c r="I2" s="184"/>
-      <c r="J2" s="184"/>
-      <c r="K2" s="184"/>
-      <c r="L2" s="184"/>
-      <c r="M2" s="184"/>
-      <c r="N2" s="184"/>
+      <c r="C2" s="183"/>
+      <c r="D2" s="183"/>
+      <c r="E2" s="183"/>
+      <c r="F2" s="183"/>
+      <c r="G2" s="183"/>
+      <c r="H2" s="184"/>
+      <c r="I2" s="183"/>
+      <c r="J2" s="183"/>
+      <c r="K2" s="183"/>
+      <c r="L2" s="183"/>
+      <c r="M2" s="183"/>
+      <c r="N2" s="183"/>
       <c r="O2" s="80"/>
       <c r="P2" s="11"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="82"/>
       <c r="B3" s="82"/>
-      <c r="C3" s="186"/>
-      <c r="D3" s="186"/>
-      <c r="E3" s="186"/>
-      <c r="F3" s="186"/>
-      <c r="G3" s="186"/>
-      <c r="H3" s="185"/>
-      <c r="I3" s="184"/>
-      <c r="J3" s="184"/>
-      <c r="K3" s="184"/>
-      <c r="L3" s="184"/>
-      <c r="M3" s="184"/>
-      <c r="N3" s="184"/>
+      <c r="C3" s="185"/>
+      <c r="D3" s="185"/>
+      <c r="E3" s="185"/>
+      <c r="F3" s="185"/>
+      <c r="G3" s="185"/>
+      <c r="H3" s="184"/>
+      <c r="I3" s="183"/>
+      <c r="J3" s="183"/>
+      <c r="K3" s="183"/>
+      <c r="L3" s="183"/>
+      <c r="M3" s="183"/>
+      <c r="N3" s="183"/>
       <c r="O3" s="80"/>
       <c r="P3" s="11"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="82"/>
       <c r="B4" s="82"/>
-      <c r="C4" s="186"/>
-      <c r="D4" s="186"/>
-      <c r="E4" s="186"/>
-      <c r="F4" s="186"/>
-      <c r="G4" s="186"/>
-      <c r="H4" s="185"/>
-      <c r="I4" s="184" t="s">
-        <v>83</v>
-      </c>
-      <c r="J4" s="184"/>
-      <c r="K4" s="184"/>
-      <c r="L4" s="184"/>
-      <c r="M4" s="184"/>
-      <c r="N4" s="184"/>
+      <c r="C4" s="185"/>
+      <c r="D4" s="185"/>
+      <c r="E4" s="185"/>
+      <c r="F4" s="185"/>
+      <c r="G4" s="185"/>
+      <c r="H4" s="184"/>
+      <c r="I4" s="183" t="s">
+        <v>78</v>
+      </c>
+      <c r="J4" s="183"/>
+      <c r="K4" s="183"/>
+      <c r="L4" s="183"/>
+      <c r="M4" s="183"/>
+      <c r="N4" s="183"/>
       <c r="O4" s="80"/>
       <c r="P4" s="11"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="82"/>
       <c r="B5" s="82"/>
-      <c r="C5" s="186"/>
-      <c r="D5" s="186"/>
-      <c r="E5" s="186"/>
-      <c r="F5" s="186"/>
-      <c r="G5" s="186"/>
-      <c r="H5" s="185"/>
-      <c r="I5" s="184"/>
-      <c r="J5" s="184"/>
-      <c r="K5" s="184"/>
-      <c r="L5" s="184"/>
-      <c r="M5" s="184"/>
-      <c r="N5" s="184"/>
+      <c r="C5" s="185"/>
+      <c r="D5" s="185"/>
+      <c r="E5" s="185"/>
+      <c r="F5" s="185"/>
+      <c r="G5" s="185"/>
+      <c r="H5" s="184"/>
+      <c r="I5" s="183"/>
+      <c r="J5" s="183"/>
+      <c r="K5" s="183"/>
+      <c r="L5" s="183"/>
+      <c r="M5" s="183"/>
+      <c r="N5" s="183"/>
       <c r="O5" s="80"/>
       <c r="P5" s="11"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="82"/>
       <c r="B6" s="82"/>
-      <c r="C6" s="184"/>
+      <c r="C6" s="183"/>
       <c r="D6" s="28"/>
-      <c r="E6" s="184"/>
-      <c r="F6" s="184"/>
-      <c r="G6" s="184"/>
-      <c r="H6" s="185"/>
-      <c r="I6" s="184"/>
-      <c r="J6" s="184"/>
-      <c r="K6" s="184"/>
-      <c r="L6" s="184"/>
-      <c r="M6" s="184"/>
-      <c r="N6" s="184"/>
+      <c r="E6" s="183"/>
+      <c r="F6" s="183"/>
+      <c r="G6" s="183"/>
+      <c r="H6" s="184"/>
+      <c r="I6" s="183"/>
+      <c r="J6" s="183"/>
+      <c r="K6" s="183"/>
+      <c r="L6" s="183"/>
+      <c r="M6" s="183"/>
+      <c r="N6" s="183"/>
       <c r="O6" s="80"/>
       <c r="P6" s="11"/>
     </row>
-    <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="83"/>
       <c r="B7" s="83" t="s">
-        <v>84</v>
-      </c>
-      <c r="C7" s="235">
+        <v>79</v>
+      </c>
+      <c r="C7" s="220">
         <v>804174.23</v>
       </c>
       <c r="D7" s="28"/>
-      <c r="E7" s="184"/>
-      <c r="F7" s="184" t="s">
-        <v>115</v>
-      </c>
-      <c r="G7" s="184"/>
-      <c r="H7" s="185"/>
-      <c r="I7" s="184"/>
-      <c r="J7" s="184" t="str">
+      <c r="E7" s="183"/>
+      <c r="F7" s="183" t="s">
+        <v>110</v>
+      </c>
+      <c r="G7" s="183"/>
+      <c r="H7" s="184"/>
+      <c r="I7" s="183"/>
+      <c r="J7" s="183" t="str">
         <f>'detalle y gastos'!C7</f>
         <v>Vto. 16/06</v>
       </c>
-      <c r="K7" s="184"/>
-      <c r="L7" s="184"/>
-      <c r="M7" s="184"/>
-      <c r="N7" s="184"/>
+      <c r="K7" s="183"/>
+      <c r="L7" s="183"/>
+      <c r="M7" s="183"/>
+      <c r="N7" s="183"/>
       <c r="O7" s="80"/>
       <c r="P7" s="11"/>
     </row>
-    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="83"/>
       <c r="B8" s="82" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C8" s="87"/>
       <c r="E8" s="84"/>
@@ -3817,61 +3840,61 @@
         <f>C8-J38</f>
         <v>-142678.16310000012</v>
       </c>
-      <c r="L8" s="234">
+      <c r="L8" s="229">
         <f>C7-J38</f>
         <v>661496.06689999986</v>
       </c>
-      <c r="M8" s="234"/>
+      <c r="M8" s="229"/>
       <c r="N8" s="86"/>
       <c r="O8" s="80"/>
       <c r="P8" s="11"/>
     </row>
-    <row r="9" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="89" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B9" s="89" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C9" s="121" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D9" s="122" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E9" s="122" t="s">
         <v>1</v>
       </c>
       <c r="F9" s="120" t="s">
+        <v>83</v>
+      </c>
+      <c r="G9" s="120" t="s">
+        <v>84</v>
+      </c>
+      <c r="H9" s="123" t="s">
+        <v>87</v>
+      </c>
+      <c r="I9" s="124" t="s">
+        <v>85</v>
+      </c>
+      <c r="J9" s="125" t="s">
+        <v>79</v>
+      </c>
+      <c r="K9" s="126" t="s">
+        <v>86</v>
+      </c>
+      <c r="L9" s="126" t="s">
+        <v>86</v>
+      </c>
+      <c r="M9" s="127" t="s">
+        <v>87</v>
+      </c>
+      <c r="N9" s="120" t="s">
         <v>88</v>
       </c>
-      <c r="G9" s="120" t="s">
-        <v>89</v>
-      </c>
-      <c r="H9" s="123" t="s">
-        <v>92</v>
-      </c>
-      <c r="I9" s="124" t="s">
-        <v>90</v>
-      </c>
-      <c r="J9" s="125" t="s">
-        <v>84</v>
-      </c>
-      <c r="K9" s="126" t="s">
-        <v>91</v>
-      </c>
-      <c r="L9" s="126" t="s">
-        <v>91</v>
-      </c>
-      <c r="M9" s="127" t="s">
-        <v>92</v>
-      </c>
-      <c r="N9" s="120" t="s">
-        <v>93</v>
-      </c>
       <c r="P9" s="11"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="100">
         <v>1</v>
       </c>
@@ -3879,10 +3902,10 @@
         <v>1</v>
       </c>
       <c r="C10" s="117" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D10" s="102" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E10" s="103">
         <v>5.1100000000000003</v>
@@ -3923,11 +3946,11 @@
       </c>
       <c r="O10" s="99">
         <f>N10+'prorrateo '!L3</f>
-        <v>116652.60309958996</v>
+        <v>167752.60309958996</v>
       </c>
       <c r="P10" s="11"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="101">
         <v>2</v>
       </c>
@@ -3935,10 +3958,10 @@
         <v>2</v>
       </c>
       <c r="C11" s="117" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D11" s="102" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E11" s="103">
         <v>5.09</v>
@@ -3979,11 +4002,11 @@
       </c>
       <c r="O11" s="99">
         <f>N11+'prorrateo '!L4</f>
-        <v>111909.49404421001</v>
+        <v>162809.49404421001</v>
       </c>
       <c r="P11" s="11"/>
     </row>
-    <row r="12" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="100">
         <v>3</v>
       </c>
@@ -3991,10 +4014,10 @@
         <v>3</v>
       </c>
       <c r="C12" s="117" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D12" s="102" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E12" s="103">
         <v>5.04</v>
@@ -4035,27 +4058,27 @@
       </c>
       <c r="O12" s="99">
         <f>N12+'prorrateo '!L5</f>
-        <v>109566.41255575998</v>
+        <v>235243.42609111997</v>
       </c>
       <c r="P12" s="11"/>
       <c r="S12">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="100">
         <v>4</v>
       </c>
       <c r="B13" s="91" t="s">
-        <v>97</v>
-      </c>
-      <c r="C13" s="187" t="s">
-        <v>44</v>
+        <v>92</v>
+      </c>
+      <c r="C13" s="186" t="s">
+        <v>40</v>
       </c>
       <c r="D13" s="102" t="s">
-        <v>98</v>
-      </c>
-      <c r="E13" s="188">
+        <v>93</v>
+      </c>
+      <c r="E13" s="187">
         <v>5.21</v>
       </c>
       <c r="F13" s="104">
@@ -4068,7 +4091,7 @@
         <f t="shared" si="1"/>
         <v>55.199999999999932</v>
       </c>
-      <c r="I13" s="189">
+      <c r="I13" s="188">
         <f t="shared" si="0"/>
         <v>3.8639999999999954</v>
       </c>
@@ -4076,7 +4099,7 @@
         <f t="shared" si="2"/>
         <v>5177.0423999999939</v>
       </c>
-      <c r="K13" s="190">
+      <c r="K13" s="189">
         <f>K8*E13%</f>
         <v>-7433.5322975100062</v>
       </c>
@@ -4084,7 +4107,7 @@
         <f t="shared" si="3"/>
         <v>34463.945085489991</v>
       </c>
-      <c r="M13" s="191">
+      <c r="M13" s="190">
         <f t="shared" si="4"/>
         <v>55.199999999999932</v>
       </c>
@@ -4094,11 +4117,11 @@
       </c>
       <c r="O13" s="99">
         <f>N13+'prorrateo '!L6</f>
-        <v>114464.17897648999</v>
+        <v>166564.17897648999</v>
       </c>
       <c r="P13" s="11"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="100">
         <v>6</v>
       </c>
@@ -4106,10 +4129,10 @@
         <v>6</v>
       </c>
       <c r="C14" s="117" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D14" s="102" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E14" s="103">
         <v>5.1100000000000003</v>
@@ -4150,11 +4173,11 @@
       </c>
       <c r="O14" s="99">
         <f>N14+'prorrateo '!L7</f>
-        <v>114851.89269959001</v>
+        <v>242274.42031183001</v>
       </c>
       <c r="P14" s="11"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="100">
         <v>7</v>
       </c>
@@ -4162,10 +4185,10 @@
         <v>7</v>
       </c>
       <c r="C15" s="117" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D15" s="102" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E15" s="103">
         <v>5.09</v>
@@ -4206,10 +4229,10 @@
       </c>
       <c r="O15" s="99">
         <f>N15+'prorrateo '!L8</f>
-        <v>115023.22244421</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+        <v>165923.22244421</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="100">
         <v>8</v>
       </c>
@@ -4217,10 +4240,10 @@
         <v>8</v>
       </c>
       <c r="C16" s="117" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D16" s="102" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E16" s="103">
         <v>5.1100000000000003</v>
@@ -4261,65 +4284,65 @@
       </c>
       <c r="O16" s="99">
         <f>N16+'prorrateo '!L9</f>
-        <v>113088.69709959</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+        <v>164188.69709959</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="100">
         <v>9</v>
       </c>
       <c r="B17" s="91">
         <v>9</v>
       </c>
-      <c r="C17" s="206" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" s="207" t="s">
-        <v>101</v>
-      </c>
-      <c r="E17" s="208">
+      <c r="C17" s="204" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="205" t="s">
+        <v>96</v>
+      </c>
+      <c r="E17" s="206">
         <v>5.09</v>
       </c>
-      <c r="F17" s="209">
+      <c r="F17" s="207">
         <v>2922.7</v>
       </c>
-      <c r="G17" s="210">
+      <c r="G17" s="208">
         <v>3022.6</v>
       </c>
-      <c r="H17" s="211">
+      <c r="H17" s="209">
         <f t="shared" si="1"/>
         <v>99.900000000000091</v>
       </c>
-      <c r="I17" s="212">
+      <c r="I17" s="210">
         <f t="shared" si="0"/>
         <v>6.9930000000000074</v>
       </c>
-      <c r="J17" s="213">
+      <c r="J17" s="211">
         <f t="shared" si="2"/>
         <v>9369.3213000000087</v>
       </c>
-      <c r="K17" s="214">
+      <c r="K17" s="212">
         <f>K8*E17%</f>
         <v>-7262.3185017900059</v>
       </c>
-      <c r="L17" s="215">
+      <c r="L17" s="213">
         <f t="shared" si="3"/>
         <v>33670.149805209992</v>
       </c>
-      <c r="M17" s="216">
+      <c r="M17" s="214">
         <f t="shared" si="4"/>
         <v>99.900000000000091</v>
       </c>
-      <c r="N17" s="211">
+      <c r="N17" s="209">
         <f t="shared" si="5"/>
         <v>43039.471105210003</v>
       </c>
       <c r="O17" s="99">
         <f>N17+'prorrateo '!L10</f>
-        <v>383425.72030401957</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+        <v>521040.98691097199</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="100">
         <v>10</v>
       </c>
@@ -4327,10 +4350,10 @@
         <v>10</v>
       </c>
       <c r="C18" s="117" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D18" s="102" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E18" s="103">
         <v>5.04</v>
@@ -4371,10 +4394,10 @@
       </c>
       <c r="O18" s="99">
         <f>N18+'prorrateo '!L11</f>
-        <v>112183.06985575997</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>162583.06985575997</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="100">
         <v>11</v>
       </c>
@@ -4382,10 +4405,10 @@
         <v>11</v>
       </c>
       <c r="C19" s="117" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D19" s="110" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E19" s="103">
         <v>5.21</v>
@@ -4426,10 +4449,10 @@
       </c>
       <c r="O19" s="99">
         <f>N19+'prorrateo '!L12</f>
-        <v>126628.35287649001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>178728.35287649001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="100">
         <v>12</v>
       </c>
@@ -4437,10 +4460,10 @@
         <v>12</v>
       </c>
       <c r="C20" s="117" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D20" s="110" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E20" s="103">
         <v>5.1100000000000003</v>
@@ -4481,10 +4504,10 @@
       </c>
       <c r="O20" s="99">
         <f>N20+'prorrateo '!L13</f>
-        <v>125018.40349959003</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+        <v>176118.40349959003</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="100">
         <v>13</v>
       </c>
@@ -4492,10 +4515,10 @@
         <v>13</v>
       </c>
       <c r="C21" s="117" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D21" s="102" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="E21" s="103">
         <v>5.09</v>
@@ -4536,10 +4559,10 @@
       </c>
       <c r="O21" s="99">
         <f>N21+'prorrateo '!L14</f>
-        <v>106779.34514420998</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+        <v>233703.15444876999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="100">
         <v>14</v>
       </c>
@@ -4547,10 +4570,10 @@
         <v>14</v>
       </c>
       <c r="C22" s="153" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D22" s="154" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E22" s="155">
         <v>5.04</v>
@@ -4591,10 +4614,10 @@
       </c>
       <c r="O22" s="99">
         <f>N22+'prorrateo '!L15</f>
-        <v>254536.19184421081</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+        <v>163052.00485575999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="100">
         <v>15</v>
       </c>
@@ -4602,10 +4625,10 @@
         <v>15</v>
       </c>
       <c r="C23" s="117" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D23" s="102" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E23" s="103">
         <v>5.21</v>
@@ -4646,10 +4669,10 @@
       </c>
       <c r="O23" s="99">
         <f>N23+'prorrateo '!L16</f>
-        <v>121198.08557649</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+        <v>251114.20472713001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="100">
         <v>16</v>
       </c>
@@ -4657,10 +4680,10 @@
         <v>16</v>
       </c>
       <c r="C24" s="117" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D24" s="102" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E24" s="103">
         <v>5.04</v>
@@ -4701,10 +4724,10 @@
       </c>
       <c r="O24" s="99">
         <f>N24+'prorrateo '!L17</f>
-        <v>110269.81505575999</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+        <v>160669.81505575997</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="100">
         <v>17</v>
       </c>
@@ -4712,10 +4735,10 @@
         <v>17</v>
       </c>
       <c r="C25" s="117" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D25" s="102" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E25" s="103">
         <v>5.21</v>
@@ -4756,10 +4779,10 @@
       </c>
       <c r="O25" s="99">
         <f>N25+'prorrateo '!L18</f>
-        <v>117812.37487649001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+        <v>169912.37487649001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="100">
         <v>18</v>
       </c>
@@ -4767,10 +4790,10 @@
         <v>18</v>
       </c>
       <c r="C26" s="117" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D26" s="102" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E26" s="103">
         <v>7.4</v>
@@ -4811,60 +4834,60 @@
       </c>
       <c r="O26" s="99">
         <f>N26+'prorrateo '!L19</f>
-        <v>169537.38769060001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>243537.38769060001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="100">
         <v>19</v>
       </c>
       <c r="B27" s="92">
         <v>19</v>
       </c>
-      <c r="C27" s="217" t="s">
-        <v>71</v>
-      </c>
-      <c r="D27" s="218" t="s">
-        <v>103</v>
-      </c>
-      <c r="E27" s="219">
+      <c r="C27" s="215" t="s">
+        <v>67</v>
+      </c>
+      <c r="D27" s="216" t="s">
+        <v>98</v>
+      </c>
+      <c r="E27" s="217">
         <v>1.08</v>
       </c>
-      <c r="F27" s="209"/>
-      <c r="G27" s="210"/>
-      <c r="H27" s="211">
+      <c r="F27" s="207"/>
+      <c r="G27" s="208"/>
+      <c r="H27" s="209">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I27" s="212">
+      <c r="I27" s="210">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J27" s="213"/>
-      <c r="K27" s="214"/>
-      <c r="L27" s="215">
+      <c r="J27" s="211"/>
+      <c r="K27" s="212"/>
+      <c r="L27" s="213">
         <f t="shared" si="3"/>
         <v>7144.1575225199995</v>
       </c>
-      <c r="M27" s="216">
-        <v>0</v>
-      </c>
-      <c r="N27" s="211">
+      <c r="M27" s="214">
+        <v>0</v>
+      </c>
+      <c r="N27" s="209">
         <f t="shared" ref="N27:N37" si="6">J27+L27</f>
         <v>7144.1575225199995</v>
       </c>
       <c r="O27" s="99">
         <f>N27+'prorrateo '!L20</f>
-        <v>79367.5659969236</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+        <v>108566.87600389976</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="100">
         <v>20</v>
       </c>
       <c r="B28" s="92"/>
-      <c r="C28" s="192" t="s">
-        <v>72</v>
+      <c r="C28" s="191" t="s">
+        <v>68</v>
       </c>
       <c r="D28" s="104"/>
       <c r="E28" s="104">
@@ -4875,11 +4898,11 @@
       <c r="H28" s="106">
         <v>0</v>
       </c>
-      <c r="I28" s="193">
+      <c r="I28" s="192">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J28" s="194"/>
+      <c r="J28" s="193"/>
       <c r="K28" s="108"/>
       <c r="L28" s="129">
         <f t="shared" si="3"/>
@@ -4894,14 +4917,14 @@
       </c>
       <c r="O28" s="99">
         <f>N28+'prorrateo '!L21</f>
-        <v>22654.53119052</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+        <v>49585.319805239997</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="100"/>
       <c r="B29" s="92"/>
       <c r="C29" s="180" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D29" s="156"/>
       <c r="E29" s="156">
@@ -4926,14 +4949,14 @@
       </c>
       <c r="O29" s="99">
         <f>N29+'prorrateo '!L22</f>
-        <v>79367.5659969236</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+        <v>108566.87600389976</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="100"/>
       <c r="B30" s="92"/>
-      <c r="C30" s="192" t="s">
-        <v>74</v>
+      <c r="C30" s="191" t="s">
+        <v>70</v>
       </c>
       <c r="D30" s="104"/>
       <c r="E30" s="104">
@@ -4942,8 +4965,8 @@
       <c r="F30" s="104"/>
       <c r="G30" s="104"/>
       <c r="H30" s="106"/>
-      <c r="I30" s="193"/>
-      <c r="J30" s="194"/>
+      <c r="I30" s="192"/>
+      <c r="J30" s="193"/>
       <c r="K30" s="108"/>
       <c r="L30" s="129">
         <f t="shared" si="3"/>
@@ -4958,14 +4981,14 @@
       </c>
       <c r="O30" s="99">
         <f>N30+'prorrateo '!L23</f>
-        <v>22654.53119052</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+        <v>49585.319805239997</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="100"/>
       <c r="B31" s="92"/>
-      <c r="C31" s="192" t="s">
-        <v>75</v>
+      <c r="C31" s="191" t="s">
+        <v>71</v>
       </c>
       <c r="D31" s="104"/>
       <c r="E31" s="104">
@@ -4974,8 +4997,8 @@
       <c r="F31" s="104"/>
       <c r="G31" s="104"/>
       <c r="H31" s="106"/>
-      <c r="I31" s="193"/>
-      <c r="J31" s="194"/>
+      <c r="I31" s="192"/>
+      <c r="J31" s="193"/>
       <c r="K31" s="108"/>
       <c r="L31" s="129">
         <f t="shared" si="3"/>
@@ -4990,14 +5013,14 @@
       </c>
       <c r="O31" s="99">
         <f>N31+'prorrateo '!L24</f>
-        <v>22654.53119052</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+        <v>33454.53119052</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="100"/>
       <c r="B32" s="92"/>
       <c r="C32" s="132" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D32" s="111"/>
       <c r="E32" s="111">
@@ -5022,14 +5045,14 @@
       </c>
       <c r="O32" s="99">
         <f>N32+'prorrateo '!L25</f>
-        <v>22654.53119052</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+        <v>49585.319805239997</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="100"/>
       <c r="B33" s="92"/>
       <c r="C33" s="132" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D33" s="111"/>
       <c r="E33" s="111">
@@ -5054,14 +5077,14 @@
       </c>
       <c r="O33" s="99">
         <f>N33+'prorrateo '!L26</f>
-        <v>22654.53119052</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+        <v>33454.53119052</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="100"/>
       <c r="B34" s="92"/>
       <c r="C34" s="132" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D34" s="111"/>
       <c r="E34" s="111">
@@ -5086,16 +5109,16 @@
       </c>
       <c r="O34" s="99">
         <f>N34+'prorrateo '!L27</f>
-        <v>22654.53119052</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+        <v>33454.53119052</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="100">
         <v>21</v>
       </c>
       <c r="B35" s="92"/>
-      <c r="C35" s="192" t="s">
-        <v>79</v>
+      <c r="C35" s="191" t="s">
+        <v>75</v>
       </c>
       <c r="D35" s="104"/>
       <c r="E35" s="104">
@@ -5106,11 +5129,11 @@
       <c r="H35" s="106">
         <v>0</v>
       </c>
-      <c r="I35" s="193">
+      <c r="I35" s="192">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J35" s="221"/>
+      <c r="J35" s="219"/>
       <c r="K35" s="108"/>
       <c r="L35" s="129">
         <f t="shared" si="3"/>
@@ -5125,16 +5148,16 @@
       </c>
       <c r="O35" s="99">
         <f>N35+'prorrateo '!L28</f>
-        <v>22654.53119052</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+        <v>49585.319805239997</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="100">
         <v>22</v>
       </c>
       <c r="B36" s="92"/>
       <c r="C36" s="180" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D36" s="156"/>
       <c r="E36" s="156">
@@ -5149,7 +5172,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J36" s="195"/>
+      <c r="J36" s="194"/>
       <c r="K36" s="161"/>
       <c r="L36" s="162">
         <f t="shared" si="3"/>
@@ -5164,10 +5187,10 @@
       </c>
       <c r="O36" s="99">
         <f>N36+'prorrateo '!L29</f>
-        <v>42199.280113003195</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+        <v>33454.53119052</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="100">
         <v>23</v>
       </c>
@@ -5197,7 +5220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="100">
         <v>24</v>
       </c>
@@ -5225,7 +5248,7 @@
       </c>
       <c r="P38" s="44"/>
     </row>
-    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="80"/>
       <c r="C39" s="93"/>
       <c r="D39" s="94"/>
@@ -5250,41 +5273,41 @@
       <c r="N39" s="95"/>
       <c r="O39" s="81"/>
     </row>
-    <row r="40" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="97" t="s">
-        <v>110</v>
-      </c>
-      <c r="C40" s="233"/>
-      <c r="D40" s="231"/>
-      <c r="E40" s="231"/>
-      <c r="F40" s="231"/>
-      <c r="G40" s="231"/>
-      <c r="H40" s="231"/>
-      <c r="I40" s="231"/>
-      <c r="J40" s="231"/>
-      <c r="K40" s="231"/>
-      <c r="L40" s="231"/>
-      <c r="M40" s="231"/>
-      <c r="N40" s="231"/>
+        <v>105</v>
+      </c>
+      <c r="C40" s="228"/>
+      <c r="D40" s="226"/>
+      <c r="E40" s="226"/>
+      <c r="F40" s="226"/>
+      <c r="G40" s="226"/>
+      <c r="H40" s="226"/>
+      <c r="I40" s="226"/>
+      <c r="J40" s="226"/>
+      <c r="K40" s="226"/>
+      <c r="L40" s="226"/>
+      <c r="M40" s="226"/>
+      <c r="N40" s="226"/>
       <c r="O40" s="97"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="H41" s="81"/>
       <c r="J41" s="98"/>
       <c r="K41" s="98"/>
       <c r="L41" s="98"/>
       <c r="N41" s="99"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E43" s="4"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="L44" s="164"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="L45" s="98"/>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E46" s="165"/>
       <c r="F46" s="165"/>
       <c r="G46" s="165"/>

--- a/ROSALES/Mayo/expensas rosales MAYOxlsx.xlsx
+++ b/ROSALES/Mayo/expensas rosales MAYOxlsx.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\ROSALES\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{541D1DF3-A7B3-43A7-AE9B-25D2AEC08979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{854EB5E1-9975-4797-A7E7-7682808B0521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -1130,7 +1130,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="241">
+  <cellXfs count="232">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1370,16 +1370,8 @@
     <xf numFmtId="164" fontId="20" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="19" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="19" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="26" fillId="6" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="171" fontId="25" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="25" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="25" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="172" fontId="25" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="172" fontId="28" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="25" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1429,7 +1421,6 @@
     </xf>
     <xf numFmtId="172" fontId="25" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="172" fontId="25" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="25" fillId="6" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="6" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1464,29 +1455,6 @@
     <xf numFmtId="4" fontId="1" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="172" fontId="25" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="172" fontId="31" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="20" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="20" fillId="10" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1499,11 +1467,32 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="9" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="175" fontId="9" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="175" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2022,7 +2011,7 @@
         <v>10</v>
       </c>
       <c r="B19" s="39"/>
-      <c r="C19" s="234">
+      <c r="C19" s="218">
         <v>307780.02</v>
       </c>
       <c r="D19" s="20"/>
@@ -2068,7 +2057,7 @@
         <v>12</v>
       </c>
       <c r="B23" s="39"/>
-      <c r="C23" s="235"/>
+      <c r="C23" s="219"/>
     </row>
     <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="28" t="s">
@@ -2104,7 +2093,7 @@
       <c r="F26" s="12"/>
     </row>
     <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="230" t="s">
+      <c r="A27" s="214" t="s">
         <v>125</v>
       </c>
       <c r="B27" s="141"/>
@@ -2115,7 +2104,7 @@
       <c r="F27" s="12"/>
     </row>
     <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="230" t="s">
+      <c r="A28" s="214" t="s">
         <v>119</v>
       </c>
       <c r="B28" s="141"/>
@@ -2197,17 +2186,15 @@
       <c r="F37" s="12"/>
     </row>
     <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="236"/>
-      <c r="B38" s="236"/>
-      <c r="C38" s="237"/>
+      <c r="C38" s="25"/>
       <c r="F38" s="12"/>
     </row>
     <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="238" t="s">
+      <c r="A39" s="220" t="s">
         <v>128</v>
       </c>
-      <c r="B39" s="238"/>
-      <c r="C39" s="239">
+      <c r="B39" s="220"/>
+      <c r="C39" s="221">
         <v>1000000</v>
       </c>
       <c r="F39" s="12"/>
@@ -2242,33 +2229,33 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="4"/>
-      <c r="C46" s="169"/>
+      <c r="C46" s="163"/>
       <c r="D46" s="5"/>
       <c r="E46" s="5"/>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4"/>
-      <c r="C47" s="169"/>
+      <c r="C47" s="163"/>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
     </row>
     <row r="48" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="170" t="s">
+      <c r="A48" s="164" t="s">
         <v>126</v>
       </c>
-      <c r="B48" s="168"/>
-      <c r="C48" s="171">
+      <c r="B48" s="162"/>
+      <c r="C48" s="165">
         <v>-664175.24157355423</v>
       </c>
       <c r="D48" s="6"/>
       <c r="E48" s="6"/>
     </row>
     <row r="49" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="170" t="s">
+      <c r="A49" s="164" t="s">
         <v>121</v>
       </c>
-      <c r="B49" s="168"/>
-      <c r="C49" s="173">
+      <c r="B49" s="162"/>
+      <c r="C49" s="167">
         <f>-(C32-C30)</f>
         <v>-1046075.3500000001</v>
       </c>
@@ -2276,25 +2263,25 @@
       <c r="E49" s="6"/>
     </row>
     <row r="50" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="170" t="s">
+      <c r="A50" s="164" t="s">
         <v>113</v>
       </c>
-      <c r="B50" s="168"/>
-      <c r="C50" s="218">
+      <c r="B50" s="162"/>
+      <c r="C50" s="211">
         <f>'prorrateo '!F31</f>
         <v>1137720.7895689341</v>
       </c>
     </row>
     <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="174"/>
-      <c r="C51" s="175"/>
+      <c r="A51" s="168"/>
+      <c r="C51" s="169"/>
     </row>
     <row r="52" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="172" t="s">
+      <c r="A52" s="166" t="s">
         <v>8</v>
       </c>
-      <c r="B52" s="167"/>
-      <c r="C52" s="176">
+      <c r="B52" s="161"/>
+      <c r="C52" s="170">
         <f>SUM(C46:C50)</f>
         <v>-572529.8020046202</v>
       </c>
@@ -2306,15 +2293,15 @@
       <c r="C53" s="10"/>
     </row>
     <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="221"/>
-      <c r="B54" s="221"/>
-      <c r="C54" s="221"/>
+      <c r="A54" s="222"/>
+      <c r="B54" s="222"/>
+      <c r="C54" s="222"/>
       <c r="F54" s="44"/>
     </row>
     <row r="55" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="222"/>
-      <c r="B55" s="222"/>
-      <c r="C55" s="222"/>
+      <c r="A55" s="223"/>
+      <c r="B55" s="223"/>
+      <c r="C55" s="223"/>
     </row>
     <row r="56" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="26" t="s">
@@ -2344,11 +2331,11 @@
       <c r="C59" s="32"/>
     </row>
     <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="177" t="s">
-        <v>0</v>
-      </c>
-      <c r="B60" s="178"/>
-      <c r="C60" s="179">
+      <c r="A60" s="171" t="s">
+        <v>0</v>
+      </c>
+      <c r="B60" s="172"/>
+      <c r="C60" s="173">
         <f>SUM(C56:C59)</f>
         <v>0</v>
       </c>
@@ -2415,21 +2402,21 @@
       <c r="A1" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="223">
+      <c r="B1" s="224">
         <f>D1</f>
         <v>1436145.71</v>
       </c>
-      <c r="C1" s="223"/>
+      <c r="C1" s="224"/>
       <c r="D1" s="145">
         <v>1436145.71</v>
       </c>
       <c r="E1" t="s">
         <v>129</v>
       </c>
-      <c r="G1" s="240">
+      <c r="G1" s="226">
         <v>1000000</v>
       </c>
-      <c r="H1" s="240"/>
+      <c r="H1" s="226"/>
     </row>
     <row r="2" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="46" t="s">
@@ -2485,7 +2472,7 @@
       <c r="E3" s="131">
         <v>73387.045781000008</v>
       </c>
-      <c r="F3" s="231">
+      <c r="F3" s="215">
         <f>E3</f>
         <v>73387.045781000008</v>
       </c>
@@ -2527,8 +2514,8 @@
       <c r="E4" s="131">
         <v>73099.816638999997</v>
       </c>
-      <c r="F4" s="231">
-        <f t="shared" ref="F4:F23" si="0">E4</f>
+      <c r="F4" s="215">
+        <f t="shared" ref="F4:F18" si="0">E4</f>
         <v>73099.816638999997</v>
       </c>
       <c r="G4" s="56">
@@ -2569,7 +2556,7 @@
       <c r="E5" s="131">
         <v>72381.743783999991</v>
       </c>
-      <c r="F5" s="231"/>
+      <c r="F5" s="215"/>
       <c r="G5" s="56">
         <f t="shared" si="1"/>
         <v>72381.743783999991</v>
@@ -2606,7 +2593,7 @@
       <c r="E6" s="131">
         <v>74823.191491000005</v>
       </c>
-      <c r="F6" s="231">
+      <c r="F6" s="215">
         <f>E6</f>
         <v>74823.191491000005</v>
       </c>
@@ -2648,7 +2635,7 @@
       <c r="E7" s="131">
         <v>73387.045781000008</v>
       </c>
-      <c r="F7" s="231"/>
+      <c r="F7" s="215"/>
       <c r="G7" s="56">
         <f t="shared" si="1"/>
         <v>73387.045781000008</v>
@@ -2685,7 +2672,7 @@
       <c r="E8" s="131">
         <v>73099.816638999997</v>
       </c>
-      <c r="F8" s="231">
+      <c r="F8" s="215">
         <f>E8</f>
         <v>73099.816638999997</v>
       </c>
@@ -2725,7 +2712,7 @@
       <c r="E9" s="131">
         <v>73387.045781000008</v>
       </c>
-      <c r="F9" s="231">
+      <c r="F9" s="215">
         <f t="shared" si="0"/>
         <v>73387.045781000008</v>
       </c>
@@ -2752,40 +2739,40 @@
       </c>
     </row>
     <row r="10" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="233" t="s">
+      <c r="A10" s="217" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="198" t="s">
+      <c r="B10" s="191" t="s">
         <v>116</v>
       </c>
-      <c r="C10" s="199" t="s">
+      <c r="C10" s="192" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="200">
+      <c r="D10" s="193">
         <v>5.09</v>
       </c>
-      <c r="E10" s="201">
+      <c r="E10" s="194">
         <v>340386.24919880956</v>
       </c>
-      <c r="F10" s="232"/>
-      <c r="G10" s="202">
+      <c r="F10" s="216"/>
+      <c r="G10" s="195">
         <f t="shared" si="1"/>
         <v>340386.24919880956</v>
       </c>
-      <c r="H10" s="202">
+      <c r="H10" s="195">
         <f t="shared" si="2"/>
         <v>13615.449967952383</v>
       </c>
-      <c r="I10" s="202">
+      <c r="I10" s="195">
         <f t="shared" si="3"/>
         <v>73099.816638999997</v>
       </c>
-      <c r="J10" s="202">
+      <c r="J10" s="195">
         <f t="shared" si="4"/>
         <v>50900</v>
       </c>
-      <c r="K10" s="202"/>
-      <c r="L10" s="203">
+      <c r="K10" s="195"/>
+      <c r="L10" s="196">
         <f t="shared" si="5"/>
         <v>478001.51580576197</v>
       </c>
@@ -2804,7 +2791,7 @@
       <c r="E11" s="131">
         <v>72381.743783999991</v>
       </c>
-      <c r="F11" s="231">
+      <c r="F11" s="215">
         <f>E11</f>
         <v>72381.743783999991</v>
       </c>
@@ -2844,7 +2831,7 @@
       <c r="E12" s="131">
         <v>74823.191491000005</v>
       </c>
-      <c r="F12" s="231">
+      <c r="F12" s="215">
         <f t="shared" si="0"/>
         <v>74823.191491000005</v>
       </c>
@@ -2886,7 +2873,7 @@
       <c r="E13" s="131">
         <v>73387.045781000008</v>
       </c>
-      <c r="F13" s="231">
+      <c r="F13" s="215">
         <f>E13</f>
         <v>73387.045781000008</v>
       </c>
@@ -2926,7 +2913,7 @@
       <c r="E14" s="131">
         <v>73099.816638999997</v>
       </c>
-      <c r="F14" s="231"/>
+      <c r="F14" s="215"/>
       <c r="G14" s="66">
         <f t="shared" si="1"/>
         <v>73099.816638999997</v>
@@ -2965,7 +2952,7 @@
       <c r="E15" s="131">
         <v>214265.93077245081</v>
       </c>
-      <c r="F15" s="231">
+      <c r="F15" s="215">
         <f>E15</f>
         <v>214265.93077245081</v>
       </c>
@@ -3007,7 +2994,7 @@
       <c r="E16" s="131">
         <v>74823.191491000005</v>
       </c>
-      <c r="F16" s="231"/>
+      <c r="F16" s="215"/>
       <c r="G16" s="56">
         <f t="shared" si="1"/>
         <v>74823.191491000005</v>
@@ -3044,7 +3031,7 @@
       <c r="E17" s="131">
         <v>72381.743783999991</v>
       </c>
-      <c r="F17" s="231">
+      <c r="F17" s="215">
         <f t="shared" si="0"/>
         <v>72381.743783999991</v>
       </c>
@@ -3084,7 +3071,7 @@
       <c r="E18" s="131">
         <v>74823.191491000005</v>
       </c>
-      <c r="F18" s="231">
+      <c r="F18" s="215">
         <f t="shared" si="0"/>
         <v>74823.191491000005</v>
       </c>
@@ -3124,7 +3111,7 @@
       <c r="E19" s="131">
         <v>106274.78254</v>
       </c>
-      <c r="F19" s="231">
+      <c r="F19" s="215">
         <f>E19</f>
         <v>106274.78254</v>
       </c>
@@ -3151,40 +3138,40 @@
       </c>
     </row>
     <row r="20" spans="1:15" ht="24" x14ac:dyDescent="0.25">
-      <c r="A20" s="197"/>
-      <c r="B20" s="198" t="s">
+      <c r="A20" s="190"/>
+      <c r="B20" s="191" t="s">
         <v>116</v>
       </c>
-      <c r="C20" s="199" t="s">
+      <c r="C20" s="192" t="s">
         <v>67</v>
       </c>
-      <c r="D20" s="200">
+      <c r="D20" s="193">
         <v>1.08</v>
       </c>
-      <c r="E20" s="201">
+      <c r="E20" s="194">
         <v>72223.408474403608</v>
       </c>
-      <c r="F20" s="232">
-        <v>0</v>
-      </c>
-      <c r="G20" s="202">
+      <c r="F20" s="216">
+        <v>0</v>
+      </c>
+      <c r="G20" s="195">
         <f t="shared" si="1"/>
         <v>72223.408474403608</v>
       </c>
-      <c r="H20" s="202">
+      <c r="H20" s="195">
         <f t="shared" si="2"/>
         <v>2888.9363389761443</v>
       </c>
-      <c r="I20" s="202">
+      <c r="I20" s="195">
         <f t="shared" si="3"/>
         <v>15510.373668</v>
       </c>
-      <c r="J20" s="202">
+      <c r="J20" s="195">
         <f t="shared" si="4"/>
         <v>10800</v>
       </c>
-      <c r="K20" s="202"/>
-      <c r="L20" s="203">
+      <c r="K20" s="195"/>
+      <c r="L20" s="196">
         <f t="shared" si="5"/>
         <v>101422.71848137975</v>
       </c>
@@ -3203,7 +3190,7 @@
       <c r="E21" s="131">
         <v>15510.373668</v>
       </c>
-      <c r="F21" s="195"/>
+      <c r="F21" s="188"/>
       <c r="G21" s="56">
         <f t="shared" si="1"/>
         <v>15510.373668</v>
@@ -3238,7 +3225,7 @@
       <c r="E22" s="150">
         <v>72223.408474403608</v>
       </c>
-      <c r="F22" s="196">
+      <c r="F22" s="189">
         <v>0</v>
       </c>
       <c r="G22" s="151">
@@ -3277,7 +3264,7 @@
       <c r="E23" s="131">
         <v>15510.373668</v>
       </c>
-      <c r="F23" s="195"/>
+      <c r="F23" s="188"/>
       <c r="G23" s="56">
         <f t="shared" si="1"/>
         <v>15510.373668</v>
@@ -3316,7 +3303,7 @@
       <c r="E24" s="131">
         <v>15510.373668</v>
       </c>
-      <c r="F24" s="231">
+      <c r="F24" s="215">
         <f>E24</f>
         <v>15510.373668</v>
       </c>
@@ -3356,7 +3343,7 @@
       <c r="E25" s="131">
         <v>15510.373668</v>
       </c>
-      <c r="F25" s="231"/>
+      <c r="F25" s="215"/>
       <c r="G25" s="56">
         <f t="shared" si="1"/>
         <v>15510.373668</v>
@@ -3393,8 +3380,8 @@
       <c r="E26" s="131">
         <v>15510.373668</v>
       </c>
-      <c r="F26" s="231">
-        <f t="shared" ref="F26:F28" si="6">E26</f>
+      <c r="F26" s="215">
+        <f t="shared" ref="F26:F27" si="6">E26</f>
         <v>15510.373668</v>
       </c>
       <c r="G26" s="56">
@@ -3433,7 +3420,7 @@
       <c r="E27" s="131">
         <v>15510.373668</v>
       </c>
-      <c r="F27" s="231">
+      <c r="F27" s="215">
         <f t="shared" si="6"/>
         <v>15510.373668</v>
       </c>
@@ -3478,7 +3465,7 @@
       <c r="E28" s="131">
         <v>15510.373668</v>
       </c>
-      <c r="F28" s="231"/>
+      <c r="F28" s="215"/>
       <c r="G28" s="56">
         <f t="shared" si="1"/>
         <v>15510.373668</v>
@@ -3517,7 +3504,7 @@
       <c r="E29" s="131">
         <v>35055.122590483195</v>
       </c>
-      <c r="F29" s="231">
+      <c r="F29" s="215">
         <f>E29</f>
         <v>35055.122590483195</v>
       </c>
@@ -3592,62 +3579,62 @@
       <c r="J32" s="22"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="224" t="s">
+      <c r="A33" s="225" t="s">
         <v>133</v>
       </c>
-      <c r="B33" s="224"/>
-      <c r="C33" s="224"/>
-      <c r="D33" s="224"/>
-      <c r="E33" s="224"/>
-      <c r="F33" s="224"/>
-      <c r="G33" s="224"/>
-      <c r="H33" s="224"/>
-      <c r="I33" s="224"/>
-      <c r="J33" s="224"/>
-      <c r="K33" s="224"/>
-      <c r="L33" s="224"/>
+      <c r="B33" s="225"/>
+      <c r="C33" s="225"/>
+      <c r="D33" s="225"/>
+      <c r="E33" s="225"/>
+      <c r="F33" s="225"/>
+      <c r="G33" s="225"/>
+      <c r="H33" s="225"/>
+      <c r="I33" s="225"/>
+      <c r="J33" s="225"/>
+      <c r="K33" s="225"/>
+      <c r="L33" s="225"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="224"/>
-      <c r="B34" s="224"/>
-      <c r="C34" s="224"/>
-      <c r="D34" s="224"/>
-      <c r="E34" s="224"/>
-      <c r="F34" s="224"/>
-      <c r="G34" s="224"/>
-      <c r="H34" s="224"/>
-      <c r="I34" s="224"/>
-      <c r="J34" s="224"/>
-      <c r="K34" s="224"/>
-      <c r="L34" s="224"/>
+      <c r="A34" s="225"/>
+      <c r="B34" s="225"/>
+      <c r="C34" s="225"/>
+      <c r="D34" s="225"/>
+      <c r="E34" s="225"/>
+      <c r="F34" s="225"/>
+      <c r="G34" s="225"/>
+      <c r="H34" s="225"/>
+      <c r="I34" s="225"/>
+      <c r="J34" s="225"/>
+      <c r="K34" s="225"/>
+      <c r="L34" s="225"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="224"/>
-      <c r="B35" s="224"/>
-      <c r="C35" s="224"/>
-      <c r="D35" s="224"/>
-      <c r="E35" s="224"/>
-      <c r="F35" s="224"/>
-      <c r="G35" s="224"/>
-      <c r="H35" s="224"/>
-      <c r="I35" s="224"/>
-      <c r="J35" s="224"/>
-      <c r="K35" s="224"/>
-      <c r="L35" s="224"/>
+      <c r="A35" s="225"/>
+      <c r="B35" s="225"/>
+      <c r="C35" s="225"/>
+      <c r="D35" s="225"/>
+      <c r="E35" s="225"/>
+      <c r="F35" s="225"/>
+      <c r="G35" s="225"/>
+      <c r="H35" s="225"/>
+      <c r="I35" s="225"/>
+      <c r="J35" s="225"/>
+      <c r="K35" s="225"/>
+      <c r="L35" s="225"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="224"/>
-      <c r="B36" s="224"/>
-      <c r="C36" s="224"/>
-      <c r="D36" s="224"/>
-      <c r="E36" s="224"/>
-      <c r="F36" s="224"/>
-      <c r="G36" s="224"/>
-      <c r="H36" s="224"/>
-      <c r="I36" s="224"/>
-      <c r="J36" s="224"/>
-      <c r="K36" s="224"/>
-      <c r="L36" s="224"/>
+      <c r="A36" s="225"/>
+      <c r="B36" s="225"/>
+      <c r="C36" s="225"/>
+      <c r="D36" s="225"/>
+      <c r="E36" s="225"/>
+      <c r="F36" s="225"/>
+      <c r="G36" s="225"/>
+      <c r="H36" s="225"/>
+      <c r="I36" s="225"/>
+      <c r="J36" s="225"/>
+      <c r="K36" s="225"/>
+      <c r="L36" s="225"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E40" s="21"/>
@@ -3687,113 +3674,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="225" t="s">
+      <c r="A1" s="227" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="226"/>
-      <c r="C1" s="226"/>
-      <c r="D1" s="226"/>
-      <c r="E1" s="226"/>
-      <c r="F1" s="226"/>
-      <c r="G1" s="226"/>
-      <c r="H1" s="226"/>
-      <c r="I1" s="226"/>
-      <c r="J1" s="226"/>
-      <c r="K1" s="226"/>
-      <c r="L1" s="226"/>
-      <c r="M1" s="226"/>
-      <c r="N1" s="227"/>
+      <c r="B1" s="228"/>
+      <c r="C1" s="228"/>
+      <c r="D1" s="228"/>
+      <c r="E1" s="228"/>
+      <c r="F1" s="228"/>
+      <c r="G1" s="228"/>
+      <c r="H1" s="228"/>
+      <c r="I1" s="228"/>
+      <c r="J1" s="228"/>
+      <c r="K1" s="228"/>
+      <c r="L1" s="228"/>
+      <c r="M1" s="228"/>
+      <c r="N1" s="229"/>
       <c r="O1" s="78"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="79"/>
       <c r="B2" s="79"/>
-      <c r="C2" s="183"/>
-      <c r="D2" s="183"/>
-      <c r="E2" s="183"/>
-      <c r="F2" s="183"/>
-      <c r="G2" s="183"/>
-      <c r="H2" s="184"/>
-      <c r="I2" s="183"/>
-      <c r="J2" s="183"/>
-      <c r="K2" s="183"/>
-      <c r="L2" s="183"/>
-      <c r="M2" s="183"/>
-      <c r="N2" s="183"/>
+      <c r="C2" s="177"/>
+      <c r="D2" s="177"/>
+      <c r="E2" s="177"/>
+      <c r="F2" s="177"/>
+      <c r="G2" s="177"/>
+      <c r="H2" s="178"/>
+      <c r="I2" s="177"/>
+      <c r="J2" s="177"/>
+      <c r="K2" s="177"/>
+      <c r="L2" s="177"/>
+      <c r="M2" s="177"/>
+      <c r="N2" s="177"/>
       <c r="O2" s="80"/>
       <c r="P2" s="11"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="82"/>
       <c r="B3" s="82"/>
-      <c r="C3" s="185"/>
-      <c r="D3" s="185"/>
-      <c r="E3" s="185"/>
-      <c r="F3" s="185"/>
-      <c r="G3" s="185"/>
-      <c r="H3" s="184"/>
-      <c r="I3" s="183"/>
-      <c r="J3" s="183"/>
-      <c r="K3" s="183"/>
-      <c r="L3" s="183"/>
-      <c r="M3" s="183"/>
-      <c r="N3" s="183"/>
+      <c r="C3" s="179"/>
+      <c r="D3" s="179"/>
+      <c r="E3" s="179"/>
+      <c r="F3" s="179"/>
+      <c r="G3" s="179"/>
+      <c r="H3" s="178"/>
+      <c r="I3" s="177"/>
+      <c r="J3" s="177"/>
+      <c r="K3" s="177"/>
+      <c r="L3" s="177"/>
+      <c r="M3" s="177"/>
+      <c r="N3" s="177"/>
       <c r="O3" s="80"/>
       <c r="P3" s="11"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="82"/>
       <c r="B4" s="82"/>
-      <c r="C4" s="185"/>
-      <c r="D4" s="185"/>
-      <c r="E4" s="185"/>
-      <c r="F4" s="185"/>
-      <c r="G4" s="185"/>
-      <c r="H4" s="184"/>
-      <c r="I4" s="183" t="s">
+      <c r="C4" s="179"/>
+      <c r="D4" s="179"/>
+      <c r="E4" s="179"/>
+      <c r="F4" s="179"/>
+      <c r="G4" s="179"/>
+      <c r="H4" s="178"/>
+      <c r="I4" s="177" t="s">
         <v>78</v>
       </c>
-      <c r="J4" s="183"/>
-      <c r="K4" s="183"/>
-      <c r="L4" s="183"/>
-      <c r="M4" s="183"/>
-      <c r="N4" s="183"/>
+      <c r="J4" s="177"/>
+      <c r="K4" s="177"/>
+      <c r="L4" s="177"/>
+      <c r="M4" s="177"/>
+      <c r="N4" s="177"/>
       <c r="O4" s="80"/>
       <c r="P4" s="11"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="82"/>
       <c r="B5" s="82"/>
-      <c r="C5" s="185"/>
-      <c r="D5" s="185"/>
-      <c r="E5" s="185"/>
-      <c r="F5" s="185"/>
-      <c r="G5" s="185"/>
-      <c r="H5" s="184"/>
-      <c r="I5" s="183"/>
-      <c r="J5" s="183"/>
-      <c r="K5" s="183"/>
-      <c r="L5" s="183"/>
-      <c r="M5" s="183"/>
-      <c r="N5" s="183"/>
+      <c r="C5" s="179"/>
+      <c r="D5" s="179"/>
+      <c r="E5" s="179"/>
+      <c r="F5" s="179"/>
+      <c r="G5" s="179"/>
+      <c r="H5" s="178"/>
+      <c r="I5" s="177"/>
+      <c r="J5" s="177"/>
+      <c r="K5" s="177"/>
+      <c r="L5" s="177"/>
+      <c r="M5" s="177"/>
+      <c r="N5" s="177"/>
       <c r="O5" s="80"/>
       <c r="P5" s="11"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="82"/>
       <c r="B6" s="82"/>
-      <c r="C6" s="183"/>
+      <c r="C6" s="177"/>
       <c r="D6" s="28"/>
-      <c r="E6" s="183"/>
-      <c r="F6" s="183"/>
-      <c r="G6" s="183"/>
-      <c r="H6" s="184"/>
-      <c r="I6" s="183"/>
-      <c r="J6" s="183"/>
-      <c r="K6" s="183"/>
-      <c r="L6" s="183"/>
-      <c r="M6" s="183"/>
-      <c r="N6" s="183"/>
+      <c r="E6" s="177"/>
+      <c r="F6" s="177"/>
+      <c r="G6" s="177"/>
+      <c r="H6" s="178"/>
+      <c r="I6" s="177"/>
+      <c r="J6" s="177"/>
+      <c r="K6" s="177"/>
+      <c r="L6" s="177"/>
+      <c r="M6" s="177"/>
+      <c r="N6" s="177"/>
       <c r="O6" s="80"/>
       <c r="P6" s="11"/>
     </row>
@@ -3802,25 +3789,25 @@
       <c r="B7" s="83" t="s">
         <v>79</v>
       </c>
-      <c r="C7" s="220">
+      <c r="C7" s="213">
         <v>804174.23</v>
       </c>
       <c r="D7" s="28"/>
-      <c r="E7" s="183"/>
-      <c r="F7" s="183" t="s">
+      <c r="E7" s="177"/>
+      <c r="F7" s="177" t="s">
         <v>110</v>
       </c>
-      <c r="G7" s="183"/>
-      <c r="H7" s="184"/>
-      <c r="I7" s="183"/>
-      <c r="J7" s="183" t="str">
+      <c r="G7" s="177"/>
+      <c r="H7" s="178"/>
+      <c r="I7" s="177"/>
+      <c r="J7" s="177" t="str">
         <f>'detalle y gastos'!C7</f>
         <v>Vto. 16/06</v>
       </c>
-      <c r="K7" s="183"/>
-      <c r="L7" s="183"/>
-      <c r="M7" s="183"/>
-      <c r="N7" s="183"/>
+      <c r="K7" s="177"/>
+      <c r="L7" s="177"/>
+      <c r="M7" s="177"/>
+      <c r="N7" s="177"/>
       <c r="O7" s="80"/>
       <c r="P7" s="11"/>
     </row>
@@ -3838,13 +3825,13 @@
       <c r="J8" s="80"/>
       <c r="K8" s="88">
         <f>C8-J38</f>
-        <v>-142678.16310000012</v>
-      </c>
-      <c r="L8" s="229">
+        <v>-159634.85269999999</v>
+      </c>
+      <c r="L8" s="231">
         <f>C7-J38</f>
-        <v>661496.06689999986</v>
-      </c>
-      <c r="M8" s="229"/>
+        <v>644539.37730000005</v>
+      </c>
+      <c r="M8" s="231"/>
       <c r="N8" s="86"/>
       <c r="O8" s="80"/>
       <c r="P8" s="11"/>
@@ -3911,42 +3898,42 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="F10" s="104">
-        <v>2907.8</v>
+        <v>3008.7</v>
       </c>
       <c r="G10" s="105">
-        <v>3008.7</v>
+        <v>3122.7</v>
       </c>
       <c r="H10" s="106">
         <f>G10-F10</f>
-        <v>100.89999999999964</v>
+        <v>114</v>
       </c>
       <c r="I10" s="107">
         <f t="shared" ref="I10:I37" si="0">H10*7%</f>
-        <v>7.0629999999999749</v>
+        <v>7.98</v>
       </c>
       <c r="J10" s="118">
         <f>M10*93.787</f>
-        <v>9463.1082999999671</v>
+        <v>10691.718000000001</v>
       </c>
       <c r="K10" s="108">
         <f>K8*E10%</f>
-        <v>-7290.8541344100067</v>
+        <v>-8157.3409729700006</v>
       </c>
       <c r="L10" s="129">
         <f>L$8*E10/S$12</f>
-        <v>33802.449018589992</v>
+        <v>32935.962180030008</v>
       </c>
       <c r="M10" s="109">
         <f>G10-F10</f>
-        <v>100.89999999999964</v>
+        <v>114</v>
       </c>
       <c r="N10" s="106">
         <f>J10+L10</f>
-        <v>43265.557318589956</v>
+        <v>43627.680180030009</v>
       </c>
       <c r="O10" s="99">
         <f>N10+'prorrateo '!L3</f>
-        <v>167752.60309958996</v>
+        <v>168114.72596103002</v>
       </c>
       <c r="P10" s="11"/>
     </row>
@@ -3967,42 +3954,42 @@
         <v>5.09</v>
       </c>
       <c r="F11" s="104">
-        <v>2970</v>
+        <v>3024.8</v>
       </c>
       <c r="G11" s="105">
-        <v>3024.8</v>
+        <v>3093.6</v>
       </c>
       <c r="H11" s="106">
         <f t="shared" ref="H11:H27" si="1">G11-F11</f>
-        <v>54.800000000000182</v>
+        <v>68.799999999999727</v>
       </c>
       <c r="I11" s="107">
         <f t="shared" si="0"/>
-        <v>3.8360000000000132</v>
+        <v>4.8159999999999812</v>
       </c>
       <c r="J11" s="118">
         <f t="shared" ref="J11:J26" si="2">M11*93.787</f>
-        <v>5139.5276000000176</v>
+        <v>6452.5455999999749</v>
       </c>
       <c r="K11" s="108">
         <f>K8*E11%</f>
-        <v>-7262.3185017900059</v>
+        <v>-8125.4140024299995</v>
       </c>
       <c r="L11" s="129">
         <f t="shared" ref="L11:L36" si="3">L$8*E11/S$12</f>
-        <v>33670.149805209992</v>
+        <v>32807.054304570003</v>
       </c>
       <c r="M11" s="109">
         <f t="shared" ref="M11:M26" si="4">G11-F11</f>
-        <v>54.800000000000182</v>
+        <v>68.799999999999727</v>
       </c>
       <c r="N11" s="106">
         <f t="shared" ref="N11:N25" si="5">J11+L11</f>
-        <v>38809.677405210008</v>
+        <v>39259.599904569979</v>
       </c>
       <c r="O11" s="99">
         <f>N11+'prorrateo '!L4</f>
-        <v>162809.49404421001</v>
+        <v>163259.41654356997</v>
       </c>
       <c r="P11" s="11"/>
     </row>
@@ -4023,42 +4010,42 @@
         <v>5.04</v>
       </c>
       <c r="F12" s="104">
-        <v>1229.2</v>
+        <v>1270.2</v>
       </c>
       <c r="G12" s="105">
-        <v>1270.2</v>
+        <v>1314.5</v>
       </c>
       <c r="H12" s="106">
         <f t="shared" si="1"/>
-        <v>41</v>
+        <v>44.299999999999955</v>
       </c>
       <c r="I12" s="107">
         <f t="shared" si="0"/>
-        <v>2.87</v>
+        <v>3.1009999999999973</v>
       </c>
       <c r="J12" s="118">
         <f t="shared" si="2"/>
-        <v>3845.2670000000003</v>
+        <v>4154.7640999999958</v>
       </c>
       <c r="K12" s="108">
         <f>K8*E12%</f>
-        <v>-7190.9794202400062</v>
+        <v>-8045.5965760799991</v>
       </c>
       <c r="L12" s="129">
         <f t="shared" si="3"/>
-        <v>33339.401771759993</v>
+        <v>32484.784615920005</v>
       </c>
       <c r="M12" s="109">
         <f>G12-F12</f>
-        <v>41</v>
+        <v>44.299999999999955</v>
       </c>
       <c r="N12" s="106">
         <f t="shared" si="5"/>
-        <v>37184.668771759993</v>
+        <v>36639.548715919998</v>
       </c>
       <c r="O12" s="99">
         <f>N12+'prorrateo '!L5</f>
-        <v>235243.42609111997</v>
+        <v>234698.30603527999</v>
       </c>
       <c r="P12" s="11"/>
       <c r="S12">
@@ -4072,52 +4059,52 @@
       <c r="B13" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="C13" s="186" t="s">
+      <c r="C13" s="180" t="s">
         <v>40</v>
       </c>
       <c r="D13" s="102" t="s">
         <v>93</v>
       </c>
-      <c r="E13" s="187">
+      <c r="E13" s="181">
         <v>5.21</v>
       </c>
       <c r="F13" s="104">
-        <v>651.1</v>
+        <v>706.3</v>
       </c>
       <c r="G13" s="105">
-        <v>706.3</v>
+        <v>791.8</v>
       </c>
       <c r="H13" s="106">
         <f t="shared" si="1"/>
-        <v>55.199999999999932</v>
-      </c>
-      <c r="I13" s="188">
+        <v>85.5</v>
+      </c>
+      <c r="I13" s="182">
         <f t="shared" si="0"/>
-        <v>3.8639999999999954</v>
+        <v>5.9850000000000003</v>
       </c>
       <c r="J13" s="118">
         <f t="shared" si="2"/>
-        <v>5177.0423999999939</v>
-      </c>
-      <c r="K13" s="189">
+        <v>8018.7885000000006</v>
+      </c>
+      <c r="K13" s="183">
         <f>K8*E13%</f>
-        <v>-7433.5322975100062</v>
+        <v>-8316.9758256699988</v>
       </c>
       <c r="L13" s="129">
         <f t="shared" si="3"/>
-        <v>34463.945085489991</v>
-      </c>
-      <c r="M13" s="190">
+        <v>33580.501557329997</v>
+      </c>
+      <c r="M13" s="184">
         <f t="shared" si="4"/>
-        <v>55.199999999999932</v>
+        <v>85.5</v>
       </c>
       <c r="N13" s="106">
         <f t="shared" si="5"/>
-        <v>39640.987485489983</v>
+        <v>41599.290057329999</v>
       </c>
       <c r="O13" s="99">
         <f>N13+'prorrateo '!L6</f>
-        <v>166564.17897648999</v>
+        <v>168522.48154832999</v>
       </c>
       <c r="P13" s="11"/>
     </row>
@@ -4138,42 +4125,42 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="F14" s="104">
-        <v>1270.7</v>
+        <v>1352.4</v>
       </c>
       <c r="G14" s="105">
-        <v>1352.4</v>
+        <v>1435.7</v>
       </c>
       <c r="H14" s="106">
         <f t="shared" si="1"/>
-        <v>81.700000000000045</v>
+        <v>83.299999999999955</v>
       </c>
       <c r="I14" s="107">
         <f t="shared" si="0"/>
-        <v>5.7190000000000039</v>
+        <v>5.8309999999999977</v>
       </c>
       <c r="J14" s="118">
         <f t="shared" si="2"/>
-        <v>7662.3979000000045</v>
+        <v>7812.457099999996</v>
       </c>
       <c r="K14" s="108">
         <f>K8*E14%</f>
-        <v>-7290.8541344100067</v>
+        <v>-8157.3409729700006</v>
       </c>
       <c r="L14" s="129">
         <f t="shared" si="3"/>
-        <v>33802.449018589992</v>
+        <v>32935.962180030008</v>
       </c>
       <c r="M14" s="109">
         <f t="shared" si="4"/>
-        <v>81.700000000000045</v>
+        <v>83.299999999999955</v>
       </c>
       <c r="N14" s="106">
         <f t="shared" si="5"/>
-        <v>41464.846918589996</v>
+        <v>40748.419280030008</v>
       </c>
       <c r="O14" s="99">
         <f>N14+'prorrateo '!L7</f>
-        <v>242274.42031183001</v>
+        <v>241557.99267327003</v>
       </c>
       <c r="P14" s="11"/>
     </row>
@@ -4194,42 +4181,42 @@
         <v>5.09</v>
       </c>
       <c r="F15" s="104">
-        <v>2295.1999999999998</v>
+        <v>2383.1999999999998</v>
       </c>
       <c r="G15" s="105">
-        <v>2383.1999999999998</v>
+        <v>2418</v>
       </c>
       <c r="H15" s="106">
         <f t="shared" si="1"/>
-        <v>88</v>
+        <v>34.800000000000182</v>
       </c>
       <c r="I15" s="107">
         <f t="shared" si="0"/>
-        <v>6.16</v>
+        <v>2.4360000000000128</v>
       </c>
       <c r="J15" s="118">
         <f t="shared" si="2"/>
-        <v>8253.2560000000012</v>
+        <v>3263.7876000000174</v>
       </c>
       <c r="K15" s="108">
         <f>K8*E15%</f>
-        <v>-7262.3185017900059</v>
+        <v>-8125.4140024299995</v>
       </c>
       <c r="L15" s="129">
         <f t="shared" si="3"/>
-        <v>33670.149805209992</v>
+        <v>32807.054304570003</v>
       </c>
       <c r="M15" s="109">
         <f t="shared" si="4"/>
-        <v>88</v>
+        <v>34.800000000000182</v>
       </c>
       <c r="N15" s="106">
         <f t="shared" si="5"/>
-        <v>41923.405805209994</v>
+        <v>36070.841904570021</v>
       </c>
       <c r="O15" s="99">
         <f>N15+'prorrateo '!L8</f>
-        <v>165923.22244421</v>
+        <v>160070.65854357003</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
@@ -4249,42 +4236,42 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="F16" s="104">
-        <v>1912.5</v>
+        <v>1975.4</v>
       </c>
       <c r="G16" s="105">
-        <v>1975.4</v>
+        <v>2053.3000000000002</v>
       </c>
       <c r="H16" s="106">
         <f t="shared" si="1"/>
-        <v>62.900000000000091</v>
+        <v>77.900000000000091</v>
       </c>
       <c r="I16" s="107">
         <f t="shared" si="0"/>
-        <v>4.4030000000000067</v>
+        <v>5.4530000000000065</v>
       </c>
       <c r="J16" s="118">
         <f t="shared" si="2"/>
-        <v>5899.202300000009</v>
+        <v>7306.0073000000093</v>
       </c>
       <c r="K16" s="108">
         <f>K8*E16%</f>
-        <v>-7290.8541344100067</v>
+        <v>-8157.3409729700006</v>
       </c>
       <c r="L16" s="129">
         <f t="shared" si="3"/>
-        <v>33802.449018589992</v>
+        <v>32935.962180030008</v>
       </c>
       <c r="M16" s="109">
         <f t="shared" si="4"/>
-        <v>62.900000000000091</v>
+        <v>77.900000000000091</v>
       </c>
       <c r="N16" s="106">
         <f t="shared" si="5"/>
-        <v>39701.651318590004</v>
+        <v>40241.96948003002</v>
       </c>
       <c r="O16" s="99">
         <f>N16+'prorrateo '!L9</f>
-        <v>164188.69709959</v>
+        <v>164729.01526103003</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -4294,52 +4281,52 @@
       <c r="B17" s="91">
         <v>9</v>
       </c>
-      <c r="C17" s="204" t="s">
+      <c r="C17" s="197" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="205" t="s">
+      <c r="D17" s="198" t="s">
         <v>96</v>
       </c>
-      <c r="E17" s="206">
+      <c r="E17" s="199">
         <v>5.09</v>
       </c>
-      <c r="F17" s="207">
-        <v>2922.7</v>
-      </c>
-      <c r="G17" s="208">
+      <c r="F17" s="200">
         <v>3022.6</v>
       </c>
-      <c r="H17" s="209">
+      <c r="G17" s="201">
+        <v>3139.2</v>
+      </c>
+      <c r="H17" s="202">
         <f t="shared" si="1"/>
-        <v>99.900000000000091</v>
-      </c>
-      <c r="I17" s="210">
+        <v>116.59999999999991</v>
+      </c>
+      <c r="I17" s="203">
         <f t="shared" si="0"/>
-        <v>6.9930000000000074</v>
-      </c>
-      <c r="J17" s="211">
+        <v>8.1619999999999937</v>
+      </c>
+      <c r="J17" s="204">
         <f t="shared" si="2"/>
-        <v>9369.3213000000087</v>
-      </c>
-      <c r="K17" s="212">
+        <v>10935.564199999992</v>
+      </c>
+      <c r="K17" s="205">
         <f>K8*E17%</f>
-        <v>-7262.3185017900059</v>
-      </c>
-      <c r="L17" s="213">
+        <v>-8125.4140024299995</v>
+      </c>
+      <c r="L17" s="206">
         <f t="shared" si="3"/>
-        <v>33670.149805209992</v>
-      </c>
-      <c r="M17" s="214">
+        <v>32807.054304570003</v>
+      </c>
+      <c r="M17" s="207">
         <f t="shared" si="4"/>
-        <v>99.900000000000091</v>
-      </c>
-      <c r="N17" s="209">
+        <v>116.59999999999991</v>
+      </c>
+      <c r="N17" s="202">
         <f t="shared" si="5"/>
-        <v>43039.471105210003</v>
+        <v>43742.618504569997</v>
       </c>
       <c r="O17" s="99">
         <f>N17+'prorrateo '!L10</f>
-        <v>521040.98691097199</v>
+        <v>521744.13431033195</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -4359,42 +4346,42 @@
         <v>5.04</v>
       </c>
       <c r="F18" s="104">
-        <v>1623.9</v>
+        <v>1692.8</v>
       </c>
       <c r="G18" s="105">
-        <v>1692.8</v>
+        <v>1790</v>
       </c>
       <c r="H18" s="106">
         <f t="shared" si="1"/>
-        <v>68.899999999999864</v>
+        <v>97.200000000000045</v>
       </c>
       <c r="I18" s="107">
         <f t="shared" si="0"/>
-        <v>4.8229999999999906</v>
+        <v>6.8040000000000038</v>
       </c>
       <c r="J18" s="118">
         <f t="shared" si="2"/>
-        <v>6461.9242999999879</v>
+        <v>9116.096400000004</v>
       </c>
       <c r="K18" s="108">
         <f>K8*E18%</f>
-        <v>-7190.9794202400062</v>
+        <v>-8045.5965760799991</v>
       </c>
       <c r="L18" s="129">
         <f t="shared" si="3"/>
-        <v>33339.401771759993</v>
+        <v>32484.784615920005</v>
       </c>
       <c r="M18" s="109">
         <f t="shared" si="4"/>
-        <v>68.899999999999864</v>
+        <v>97.200000000000045</v>
       </c>
       <c r="N18" s="106">
         <f t="shared" si="5"/>
-        <v>39801.326071759977</v>
+        <v>41600.881015920007</v>
       </c>
       <c r="O18" s="99">
         <f>N18+'prorrateo '!L11</f>
-        <v>162583.06985575997</v>
+        <v>164382.62479992001</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4414,42 +4401,42 @@
         <v>5.21</v>
       </c>
       <c r="F19" s="104">
-        <v>2588.5</v>
+        <v>2773.4</v>
       </c>
       <c r="G19" s="105">
-        <v>2773.4</v>
+        <v>2998.2</v>
       </c>
       <c r="H19" s="106">
         <f t="shared" si="1"/>
-        <v>184.90000000000009</v>
+        <v>224.79999999999973</v>
       </c>
       <c r="I19" s="107">
         <f t="shared" si="0"/>
-        <v>12.943000000000007</v>
+        <v>15.735999999999983</v>
       </c>
       <c r="J19" s="118">
         <f t="shared" si="2"/>
-        <v>17341.216300000011</v>
+        <v>21083.317599999977</v>
       </c>
       <c r="K19" s="108">
         <f>K8*E19%</f>
-        <v>-7433.5322975100062</v>
+        <v>-8316.9758256699988</v>
       </c>
       <c r="L19" s="129">
         <f t="shared" si="3"/>
-        <v>34463.945085489991</v>
+        <v>33580.501557329997</v>
       </c>
       <c r="M19" s="109">
         <f>G19-F19</f>
-        <v>184.90000000000009</v>
+        <v>224.79999999999973</v>
       </c>
       <c r="N19" s="106">
         <f t="shared" si="5"/>
-        <v>51805.161385490006</v>
+        <v>54663.81915732997</v>
       </c>
       <c r="O19" s="99">
         <f>N19+'prorrateo '!L12</f>
-        <v>178728.35287649001</v>
+        <v>181587.01064832998</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4469,42 +4456,42 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="F20" s="104">
-        <v>4306.2</v>
+        <v>4496.3</v>
       </c>
       <c r="G20" s="105">
-        <v>4496.3</v>
+        <v>4665.5</v>
       </c>
       <c r="H20" s="106">
         <f t="shared" si="1"/>
-        <v>190.10000000000036</v>
+        <v>169.19999999999982</v>
       </c>
       <c r="I20" s="107">
         <f t="shared" si="0"/>
-        <v>13.307000000000027</v>
+        <v>11.843999999999989</v>
       </c>
       <c r="J20" s="118">
         <f t="shared" si="2"/>
-        <v>17828.908700000036</v>
+        <v>15868.760399999985</v>
       </c>
       <c r="K20" s="108">
         <f>K8*E20%</f>
-        <v>-7290.8541344100067</v>
+        <v>-8157.3409729700006</v>
       </c>
       <c r="L20" s="129">
         <f t="shared" si="3"/>
-        <v>33802.449018589992</v>
+        <v>32935.962180030008</v>
       </c>
       <c r="M20" s="109">
         <f t="shared" si="4"/>
-        <v>190.10000000000036</v>
+        <v>169.19999999999982</v>
       </c>
       <c r="N20" s="106">
         <f t="shared" si="5"/>
-        <v>51631.357718590029</v>
+        <v>48804.722580029993</v>
       </c>
       <c r="O20" s="99">
         <f>N20+'prorrateo '!L13</f>
-        <v>176118.40349959003</v>
+        <v>173291.76836103</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -4524,42 +4511,42 @@
         <v>5.09</v>
       </c>
       <c r="F21" s="104">
-        <v>3467</v>
+        <v>3467.1</v>
       </c>
       <c r="G21" s="105">
         <v>3467.1</v>
       </c>
       <c r="H21" s="106">
         <f t="shared" si="1"/>
-        <v>9.9999999999909051E-2</v>
+        <v>0</v>
       </c>
       <c r="I21" s="107">
         <f t="shared" si="0"/>
-        <v>6.9999999999936346E-3</v>
+        <v>0</v>
       </c>
       <c r="J21" s="118">
         <f t="shared" si="2"/>
-        <v>9.3786999999914702</v>
+        <v>0</v>
       </c>
       <c r="K21" s="108">
         <f>K8*E21%</f>
-        <v>-7262.3185017900059</v>
+        <v>-8125.4140024299995</v>
       </c>
       <c r="L21" s="129">
         <f t="shared" si="3"/>
-        <v>33670.149805209992</v>
+        <v>32807.054304570003</v>
       </c>
       <c r="M21" s="109">
         <f t="shared" si="4"/>
-        <v>9.9999999999909051E-2</v>
+        <v>0</v>
       </c>
       <c r="N21" s="106">
         <f t="shared" si="5"/>
-        <v>33679.528505209986</v>
+        <v>32807.054304570003</v>
       </c>
       <c r="O21" s="99">
         <f>N21+'prorrateo '!L14</f>
-        <v>233703.15444876999</v>
+        <v>232830.68024813</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -4569,52 +4556,52 @@
       <c r="B22" s="91">
         <v>14</v>
       </c>
-      <c r="C22" s="153" t="s">
+      <c r="C22" s="117" t="s">
         <v>57</v>
       </c>
-      <c r="D22" s="154" t="s">
+      <c r="D22" s="102" t="s">
         <v>100</v>
       </c>
-      <c r="E22" s="155">
+      <c r="E22" s="103">
         <v>5.04</v>
       </c>
-      <c r="F22" s="156">
-        <v>1942</v>
-      </c>
-      <c r="G22" s="157">
+      <c r="F22" s="104">
         <v>2015.9</v>
       </c>
-      <c r="H22" s="158">
+      <c r="G22" s="105">
+        <v>2097.9</v>
+      </c>
+      <c r="H22" s="106">
         <f t="shared" si="1"/>
-        <v>73.900000000000091</v>
-      </c>
-      <c r="I22" s="159">
+        <v>82</v>
+      </c>
+      <c r="I22" s="107">
         <f t="shared" si="0"/>
-        <v>5.1730000000000071</v>
-      </c>
-      <c r="J22" s="160">
+        <v>5.74</v>
+      </c>
+      <c r="J22" s="118">
         <f t="shared" si="2"/>
-        <v>6930.8593000000092</v>
-      </c>
-      <c r="K22" s="161">
+        <v>7690.5340000000006</v>
+      </c>
+      <c r="K22" s="108">
         <f>K8*E22%</f>
-        <v>-7190.9794202400062</v>
-      </c>
-      <c r="L22" s="162">
+        <v>-8045.5965760799991</v>
+      </c>
+      <c r="L22" s="129">
         <f t="shared" si="3"/>
-        <v>33339.401771759993</v>
-      </c>
-      <c r="M22" s="163">
+        <v>32484.784615920005</v>
+      </c>
+      <c r="M22" s="109">
         <f t="shared" si="4"/>
-        <v>73.900000000000091</v>
-      </c>
-      <c r="N22" s="158">
+        <v>82</v>
+      </c>
+      <c r="N22" s="106">
         <f t="shared" si="5"/>
-        <v>40270.261071760004</v>
+        <v>40175.318615920005</v>
       </c>
       <c r="O22" s="99">
         <f>N22+'prorrateo '!L15</f>
-        <v>163052.00485575999</v>
+        <v>162957.06239991999</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
@@ -4634,42 +4621,42 @@
         <v>5.21</v>
       </c>
       <c r="F23" s="104">
-        <v>3945.7</v>
+        <v>4072.7</v>
       </c>
       <c r="G23" s="105">
-        <v>4072.7</v>
+        <v>4222.8</v>
       </c>
       <c r="H23" s="106">
         <f t="shared" si="1"/>
-        <v>127</v>
+        <v>150.10000000000036</v>
       </c>
       <c r="I23" s="107">
         <f t="shared" si="0"/>
-        <v>8.89</v>
+        <v>10.507000000000026</v>
       </c>
       <c r="J23" s="118">
         <f t="shared" si="2"/>
-        <v>11910.949000000001</v>
+        <v>14077.428700000035</v>
       </c>
       <c r="K23" s="108">
         <f>K8*E23%</f>
-        <v>-7433.5322975100062</v>
+        <v>-8316.9758256699988</v>
       </c>
       <c r="L23" s="129">
         <f t="shared" si="3"/>
-        <v>34463.945085489991</v>
+        <v>33580.501557329997</v>
       </c>
       <c r="M23" s="109">
         <f t="shared" si="4"/>
-        <v>127</v>
+        <v>150.10000000000036</v>
       </c>
       <c r="N23" s="106">
         <f t="shared" si="5"/>
-        <v>46374.894085489992</v>
+        <v>47657.93025733003</v>
       </c>
       <c r="O23" s="99">
         <f>N23+'prorrateo '!L16</f>
-        <v>251114.20472713001</v>
+        <v>252397.24089897005</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -4689,42 +4676,42 @@
         <v>5.04</v>
       </c>
       <c r="F24" s="104">
-        <v>1413.7</v>
+        <v>1462.2</v>
       </c>
       <c r="G24" s="105">
-        <v>1462.2</v>
+        <v>1529.3</v>
       </c>
       <c r="H24" s="106">
         <f t="shared" si="1"/>
-        <v>48.5</v>
+        <v>67.099999999999909</v>
       </c>
       <c r="I24" s="107">
         <f t="shared" si="0"/>
-        <v>3.3950000000000005</v>
+        <v>4.6969999999999938</v>
       </c>
       <c r="J24" s="118">
         <f t="shared" si="2"/>
-        <v>4548.6695</v>
+        <v>6293.1076999999923</v>
       </c>
       <c r="K24" s="108">
         <f>K8*E24%</f>
-        <v>-7190.9794202400062</v>
+        <v>-8045.5965760799991</v>
       </c>
       <c r="L24" s="129">
         <f t="shared" si="3"/>
-        <v>33339.401771759993</v>
+        <v>32484.784615920005</v>
       </c>
       <c r="M24" s="109">
         <f t="shared" si="4"/>
-        <v>48.5</v>
+        <v>67.099999999999909</v>
       </c>
       <c r="N24" s="106">
         <f t="shared" si="5"/>
-        <v>37888.071271759996</v>
+        <v>38777.892315919999</v>
       </c>
       <c r="O24" s="99">
         <f>N24+'prorrateo '!L17</f>
-        <v>160669.81505575997</v>
+        <v>161559.63609992</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -4744,42 +4731,42 @@
         <v>5.21</v>
       </c>
       <c r="F25" s="104">
-        <v>1261.5999999999999</v>
+        <v>1352.5</v>
       </c>
       <c r="G25" s="105">
-        <v>1352.5</v>
+        <v>1452.3</v>
       </c>
       <c r="H25" s="106">
         <f t="shared" si="1"/>
-        <v>90.900000000000091</v>
+        <v>99.799999999999955</v>
       </c>
       <c r="I25" s="107">
         <f t="shared" si="0"/>
-        <v>6.3630000000000067</v>
+        <v>6.9859999999999971</v>
       </c>
       <c r="J25" s="118">
         <f t="shared" si="2"/>
-        <v>8525.23830000001</v>
+        <v>9359.9425999999967</v>
       </c>
       <c r="K25" s="108">
         <f>K8*E25%</f>
-        <v>-7433.5322975100062</v>
+        <v>-8316.9758256699988</v>
       </c>
       <c r="L25" s="129">
         <f t="shared" si="3"/>
-        <v>34463.945085489991</v>
+        <v>33580.501557329997</v>
       </c>
       <c r="M25" s="109">
         <f t="shared" si="4"/>
-        <v>90.900000000000091</v>
+        <v>99.799999999999955</v>
       </c>
       <c r="N25" s="106">
         <f t="shared" si="5"/>
-        <v>42989.183385490003</v>
+        <v>42940.444157329992</v>
       </c>
       <c r="O25" s="99">
         <f>N25+'prorrateo '!L18</f>
-        <v>169912.37487649001</v>
+        <v>169863.63564833</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -4799,42 +4786,42 @@
         <v>7.4</v>
       </c>
       <c r="F26" s="104">
-        <v>6950</v>
+        <v>7102.6</v>
       </c>
       <c r="G26" s="105">
-        <v>7102.6</v>
+        <v>7289.3</v>
       </c>
       <c r="H26" s="106">
         <f t="shared" si="1"/>
-        <v>152.60000000000036</v>
+        <v>186.69999999999982</v>
       </c>
       <c r="I26" s="107">
         <f t="shared" si="0"/>
-        <v>10.682000000000027</v>
+        <v>13.068999999999988</v>
       </c>
       <c r="J26" s="118">
         <f t="shared" si="2"/>
-        <v>14311.896200000036</v>
+        <v>17510.032899999984</v>
       </c>
       <c r="K26" s="108">
         <f>K8*E26%</f>
-        <v>-10558.184069400011</v>
+        <v>-11812.979099800001</v>
       </c>
       <c r="L26" s="129">
         <f t="shared" si="3"/>
-        <v>48950.70895059999</v>
+        <v>47695.913920200001</v>
       </c>
       <c r="M26" s="109">
         <f t="shared" si="4"/>
-        <v>152.60000000000036</v>
+        <v>186.69999999999982</v>
       </c>
       <c r="N26" s="106">
         <f>J26+L26</f>
-        <v>63262.605150600022</v>
+        <v>65205.946820199984</v>
       </c>
       <c r="O26" s="99">
         <f>N26+'prorrateo '!L19</f>
-        <v>243537.38769060001</v>
+        <v>245480.72936019997</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4844,41 +4831,41 @@
       <c r="B27" s="92">
         <v>19</v>
       </c>
-      <c r="C27" s="215" t="s">
+      <c r="C27" s="208" t="s">
         <v>67</v>
       </c>
-      <c r="D27" s="216" t="s">
+      <c r="D27" s="209" t="s">
         <v>98</v>
       </c>
-      <c r="E27" s="217">
+      <c r="E27" s="210">
         <v>1.08</v>
       </c>
-      <c r="F27" s="207"/>
-      <c r="G27" s="208"/>
-      <c r="H27" s="209">
+      <c r="F27" s="200"/>
+      <c r="G27" s="201"/>
+      <c r="H27" s="202">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I27" s="210">
+      <c r="I27" s="203">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J27" s="211"/>
-      <c r="K27" s="212"/>
-      <c r="L27" s="213">
+      <c r="J27" s="204"/>
+      <c r="K27" s="205"/>
+      <c r="L27" s="206">
         <f t="shared" si="3"/>
-        <v>7144.1575225199995</v>
-      </c>
-      <c r="M27" s="214">
-        <v>0</v>
-      </c>
-      <c r="N27" s="209">
+        <v>6961.0252748400007</v>
+      </c>
+      <c r="M27" s="207">
+        <v>0</v>
+      </c>
+      <c r="N27" s="202">
         <f t="shared" ref="N27:N37" si="6">J27+L27</f>
-        <v>7144.1575225199995</v>
+        <v>6961.0252748400007</v>
       </c>
       <c r="O27" s="99">
         <f>N27+'prorrateo '!L20</f>
-        <v>108566.87600389976</v>
+        <v>108383.74375621974</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
@@ -4886,7 +4873,7 @@
         <v>20</v>
       </c>
       <c r="B28" s="92"/>
-      <c r="C28" s="191" t="s">
+      <c r="C28" s="185" t="s">
         <v>68</v>
       </c>
       <c r="D28" s="104"/>
@@ -4898,64 +4885,64 @@
       <c r="H28" s="106">
         <v>0</v>
       </c>
-      <c r="I28" s="192">
+      <c r="I28" s="186">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J28" s="193"/>
+      <c r="J28" s="187"/>
       <c r="K28" s="108"/>
       <c r="L28" s="129">
         <f t="shared" si="3"/>
-        <v>7144.1575225199995</v>
+        <v>6961.0252748400007</v>
       </c>
       <c r="M28" s="109">
         <v>0</v>
       </c>
       <c r="N28" s="106">
         <f t="shared" si="6"/>
-        <v>7144.1575225199995</v>
+        <v>6961.0252748400007</v>
       </c>
       <c r="O28" s="99">
         <f>N28+'prorrateo '!L21</f>
-        <v>49585.319805239997</v>
+        <v>49402.187557559999</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="100"/>
       <c r="B29" s="92"/>
-      <c r="C29" s="180" t="s">
+      <c r="C29" s="174" t="s">
         <v>69</v>
       </c>
-      <c r="D29" s="156"/>
-      <c r="E29" s="156">
+      <c r="D29" s="153"/>
+      <c r="E29" s="153">
         <v>1.08</v>
       </c>
-      <c r="F29" s="156"/>
-      <c r="G29" s="156"/>
-      <c r="H29" s="158"/>
-      <c r="I29" s="181"/>
-      <c r="J29" s="182"/>
-      <c r="K29" s="161"/>
-      <c r="L29" s="162">
+      <c r="F29" s="153"/>
+      <c r="G29" s="153"/>
+      <c r="H29" s="154"/>
+      <c r="I29" s="175"/>
+      <c r="J29" s="176"/>
+      <c r="K29" s="155"/>
+      <c r="L29" s="156">
         <f t="shared" si="3"/>
-        <v>7144.1575225199995</v>
-      </c>
-      <c r="M29" s="163">
-        <v>0</v>
-      </c>
-      <c r="N29" s="158">
+        <v>6961.0252748400007</v>
+      </c>
+      <c r="M29" s="157">
+        <v>0</v>
+      </c>
+      <c r="N29" s="154">
         <f t="shared" si="6"/>
-        <v>7144.1575225199995</v>
+        <v>6961.0252748400007</v>
       </c>
       <c r="O29" s="99">
         <f>N29+'prorrateo '!L22</f>
-        <v>108566.87600389976</v>
+        <v>108383.74375621974</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="100"/>
       <c r="B30" s="92"/>
-      <c r="C30" s="191" t="s">
+      <c r="C30" s="185" t="s">
         <v>70</v>
       </c>
       <c r="D30" s="104"/>
@@ -4965,29 +4952,29 @@
       <c r="F30" s="104"/>
       <c r="G30" s="104"/>
       <c r="H30" s="106"/>
-      <c r="I30" s="192"/>
-      <c r="J30" s="193"/>
+      <c r="I30" s="186"/>
+      <c r="J30" s="187"/>
       <c r="K30" s="108"/>
       <c r="L30" s="129">
         <f t="shared" si="3"/>
-        <v>7144.1575225199995</v>
+        <v>6961.0252748400007</v>
       </c>
       <c r="M30" s="109">
         <v>0</v>
       </c>
       <c r="N30" s="106">
         <f t="shared" si="6"/>
-        <v>7144.1575225199995</v>
+        <v>6961.0252748400007</v>
       </c>
       <c r="O30" s="99">
         <f>N30+'prorrateo '!L23</f>
-        <v>49585.319805239997</v>
+        <v>49402.187557559999</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="100"/>
       <c r="B31" s="92"/>
-      <c r="C31" s="191" t="s">
+      <c r="C31" s="185" t="s">
         <v>71</v>
       </c>
       <c r="D31" s="104"/>
@@ -4997,23 +4984,23 @@
       <c r="F31" s="104"/>
       <c r="G31" s="104"/>
       <c r="H31" s="106"/>
-      <c r="I31" s="192"/>
-      <c r="J31" s="193"/>
+      <c r="I31" s="186"/>
+      <c r="J31" s="187"/>
       <c r="K31" s="108"/>
       <c r="L31" s="129">
         <f t="shared" si="3"/>
-        <v>7144.1575225199995</v>
+        <v>6961.0252748400007</v>
       </c>
       <c r="M31" s="109">
         <v>0</v>
       </c>
       <c r="N31" s="106">
         <f t="shared" si="6"/>
-        <v>7144.1575225199995</v>
+        <v>6961.0252748400007</v>
       </c>
       <c r="O31" s="99">
         <f>N31+'prorrateo '!L24</f>
-        <v>33454.53119052</v>
+        <v>33271.398942840002</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
@@ -5034,18 +5021,18 @@
       <c r="K32" s="115"/>
       <c r="L32" s="129">
         <f t="shared" si="3"/>
-        <v>7144.1575225199995</v>
+        <v>6961.0252748400007</v>
       </c>
       <c r="M32" s="109">
         <v>0</v>
       </c>
       <c r="N32" s="106">
         <f t="shared" si="6"/>
-        <v>7144.1575225199995</v>
+        <v>6961.0252748400007</v>
       </c>
       <c r="O32" s="99">
         <f>N32+'prorrateo '!L25</f>
-        <v>49585.319805239997</v>
+        <v>49402.187557559999</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
@@ -5066,18 +5053,18 @@
       <c r="K33" s="115"/>
       <c r="L33" s="129">
         <f t="shared" si="3"/>
-        <v>7144.1575225199995</v>
+        <v>6961.0252748400007</v>
       </c>
       <c r="M33" s="109">
         <v>0</v>
       </c>
       <c r="N33" s="106">
         <f t="shared" si="6"/>
-        <v>7144.1575225199995</v>
+        <v>6961.0252748400007</v>
       </c>
       <c r="O33" s="99">
         <f>N33+'prorrateo '!L26</f>
-        <v>33454.53119052</v>
+        <v>33271.398942840002</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
@@ -5098,18 +5085,18 @@
       <c r="K34" s="115"/>
       <c r="L34" s="129">
         <f t="shared" si="3"/>
-        <v>7144.1575225199995</v>
+        <v>6961.0252748400007</v>
       </c>
       <c r="M34" s="109">
         <v>0</v>
       </c>
       <c r="N34" s="106">
         <f t="shared" si="6"/>
-        <v>7144.1575225199995</v>
+        <v>6961.0252748400007</v>
       </c>
       <c r="O34" s="99">
         <f>N34+'prorrateo '!L27</f>
-        <v>33454.53119052</v>
+        <v>33271.398942840002</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
@@ -5117,7 +5104,7 @@
         <v>21</v>
       </c>
       <c r="B35" s="92"/>
-      <c r="C35" s="191" t="s">
+      <c r="C35" s="185" t="s">
         <v>75</v>
       </c>
       <c r="D35" s="104"/>
@@ -5129,26 +5116,26 @@
       <c r="H35" s="106">
         <v>0</v>
       </c>
-      <c r="I35" s="192">
+      <c r="I35" s="186">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J35" s="219"/>
+      <c r="J35" s="212"/>
       <c r="K35" s="108"/>
       <c r="L35" s="129">
         <f t="shared" si="3"/>
-        <v>7144.1575225199995</v>
+        <v>6961.0252748400007</v>
       </c>
       <c r="M35" s="109">
         <v>0</v>
       </c>
       <c r="N35" s="106">
         <f t="shared" si="6"/>
-        <v>7144.1575225199995</v>
+        <v>6961.0252748400007</v>
       </c>
       <c r="O35" s="99">
         <f>N35+'prorrateo '!L28</f>
-        <v>49585.319805239997</v>
+        <v>49402.187557559999</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
@@ -5156,38 +5143,38 @@
         <v>22</v>
       </c>
       <c r="B36" s="92"/>
-      <c r="C36" s="180" t="s">
+      <c r="C36" s="185" t="s">
         <v>76</v>
       </c>
-      <c r="D36" s="156"/>
-      <c r="E36" s="156">
+      <c r="D36" s="104"/>
+      <c r="E36" s="104">
         <v>1.08</v>
       </c>
-      <c r="F36" s="156"/>
-      <c r="G36" s="156"/>
-      <c r="H36" s="158">
-        <v>0</v>
-      </c>
-      <c r="I36" s="181">
+      <c r="F36" s="104"/>
+      <c r="G36" s="104"/>
+      <c r="H36" s="106">
+        <v>0</v>
+      </c>
+      <c r="I36" s="186">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J36" s="194"/>
-      <c r="K36" s="161"/>
-      <c r="L36" s="162">
+      <c r="J36" s="212"/>
+      <c r="K36" s="108"/>
+      <c r="L36" s="129">
         <f t="shared" si="3"/>
-        <v>7144.1575225199995</v>
-      </c>
-      <c r="M36" s="163">
-        <v>0</v>
-      </c>
-      <c r="N36" s="158">
+        <v>6961.0252748400007</v>
+      </c>
+      <c r="M36" s="109">
+        <v>0</v>
+      </c>
+      <c r="N36" s="106">
         <f t="shared" si="6"/>
-        <v>7144.1575225199995</v>
+        <v>6961.0252748400007</v>
       </c>
       <c r="O36" s="99">
         <f>N36+'prorrateo '!L29</f>
-        <v>33454.53119052</v>
+        <v>33271.398942840002</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
@@ -5234,17 +5221,17 @@
       <c r="I38" s="114"/>
       <c r="J38" s="119">
         <f>SUM(J10:J37)</f>
-        <v>142678.16310000012</v>
+        <v>159634.85269999999</v>
       </c>
       <c r="K38" s="115"/>
       <c r="L38" s="115">
         <f>SUM(L10:L37)</f>
-        <v>661496.06690000033</v>
+        <v>644539.37729999947</v>
       </c>
       <c r="M38" s="116"/>
       <c r="N38" s="112">
         <f>SUM(N10:N37)</f>
-        <v>804174.23000000045</v>
+        <v>804174.22999999952</v>
       </c>
       <c r="P38" s="44"/>
     </row>
@@ -5261,13 +5248,13 @@
       <c r="H39" s="95"/>
       <c r="I39" s="96">
         <f>SUM(I10:I38)</f>
-        <v>106.49100000000006</v>
+        <v>119.14699999999996</v>
       </c>
       <c r="J39" s="128"/>
       <c r="K39" s="96"/>
       <c r="L39" s="135">
         <f>L38+J38</f>
-        <v>804174.23000000045</v>
+        <v>804174.22999999952</v>
       </c>
       <c r="M39" s="95"/>
       <c r="N39" s="95"/>
@@ -5277,18 +5264,18 @@
       <c r="A40" s="97" t="s">
         <v>105</v>
       </c>
-      <c r="C40" s="228"/>
-      <c r="D40" s="226"/>
-      <c r="E40" s="226"/>
-      <c r="F40" s="226"/>
-      <c r="G40" s="226"/>
-      <c r="H40" s="226"/>
-      <c r="I40" s="226"/>
-      <c r="J40" s="226"/>
-      <c r="K40" s="226"/>
-      <c r="L40" s="226"/>
-      <c r="M40" s="226"/>
-      <c r="N40" s="226"/>
+      <c r="C40" s="230"/>
+      <c r="D40" s="228"/>
+      <c r="E40" s="228"/>
+      <c r="F40" s="228"/>
+      <c r="G40" s="228"/>
+      <c r="H40" s="228"/>
+      <c r="I40" s="228"/>
+      <c r="J40" s="228"/>
+      <c r="K40" s="228"/>
+      <c r="L40" s="228"/>
+      <c r="M40" s="228"/>
+      <c r="N40" s="228"/>
       <c r="O40" s="97"/>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
@@ -5302,20 +5289,20 @@
       <c r="E43" s="4"/>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="L44" s="164"/>
+      <c r="L44" s="158"/>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="L45" s="98"/>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="E46" s="165"/>
-      <c r="F46" s="165"/>
-      <c r="G46" s="165"/>
-      <c r="H46" s="165"/>
-      <c r="I46" s="165"/>
-      <c r="J46" s="165"/>
-      <c r="K46" s="165"/>
-      <c r="L46" s="166"/>
+      <c r="E46" s="159"/>
+      <c r="F46" s="159"/>
+      <c r="G46" s="159"/>
+      <c r="H46" s="159"/>
+      <c r="I46" s="159"/>
+      <c r="J46" s="159"/>
+      <c r="K46" s="159"/>
+      <c r="L46" s="160"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/ROSALES/Mayo/expensas rosales MAYOxlsx.xlsx
+++ b/ROSALES/Mayo/expensas rosales MAYOxlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\ROSALES\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{854EB5E1-9975-4797-A7E7-7682808B0521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EE8A969-17AF-4435-BA40-6304B19AC5A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
